--- a/results/Int Task Remove ACC -0.6/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0006418092909535767 +/- 0.0017474073788414143</t>
+          <t>0.0018337408312958047 +/- 0.0013251517963740178</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.0018643031784840725 +/- 0.0015247517950203477</t>
+          <t>-0.0035757946210269397 +/- 0.0015586797066014658</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0023227383863081096 +/- 0.00120866258760914</t>
+          <t>-0.0009168704156479523 +/- 0.001339174957225341</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.00033618581907085554 +/- 0.0010714271481025634</t>
+          <t>0.0012530562347187856 +/- 0.0008584701653538035</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.0013753056234718452 +/- 0.0013955317917886197</t>
+          <t>-0.0008557457212714393 +/- 0.0013654222435017503</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.0008251833740830827 +/- 0.002538883181655268</t>
+          <t>-0.002567237163814218 +/- 0.002166264687856917</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.00033618581907094434 +/- 0.00034712153702935847</t>
+          <t>-6.112469437654643e-05 +/- 0.0001833740831295838</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0011915396509546367</t>
+          <t>-0.0015892420537897633 +/- 0.0008291356947586055</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.015250611246943801 +/- 0.0032299355049771193</t>
+          <t>0.014639364303178437 +/- 0.0024390591323629226</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.016992665036674848 +/- 0.003751084594759465</t>
+          <t>0.02555012224938872 +/- 0.002935258484973841</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.004492665036674859 +/- 0.0014596520704474015</t>
+          <t>-0.0005195599022005282 +/- 0.001093858812235534</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.004431540342298357 +/- 0.0009194137503967872</t>
+          <t>-0.001528117359413239 +/- 0.0011993531094345328</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.004798288508557513 +/- 0.002004340150619765</t>
+          <t>0.00528728606356964 +/- 0.001623260602064714</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.006479217603912024 +/- 0.001678426676986049</t>
+          <t>0.007915647921760327 +/- 0.0023651781679640506</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.007487775061124735 +/- 0.0014545237205734341</t>
+          <t>0.011430317848410709 +/- 0.0011287399335342038</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.0011308068459657261 +/- 0.0014467971122915262</t>
+          <t>-0.0021699266503667934 +/- 0.0011950620290964132</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.002689486552567277 +/- 0.0007461219814018219</t>
+          <t>-0.0019865525672371877 +/- 0.001161771259703449</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0005501222493887736 +/- 0.0013166662120133097</t>
+          <t>-0.0026894865525672884 +/- 0.0007707530692493004</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.0006723716381418443 +/- 0.0014771449845470243</t>
+          <t>0.0035146699266503157 +/- 0.001177741373349496</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0008863080684596957 +/- 0.000288324606725438</t>
+          <t>0.0003056234718825879 +/- 0.00019329325551150234</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.011674816625916906 +/- 0.0012209648139020922</t>
+          <t>0.012499999999999956 +/- 0.001105748931242377</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.00562347188264053 +/- 0.0012836185819070705</t>
+          <t>-0.0014364303178484694 +/- 0.0014723948007880276</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.0012224938875305292 +/- 0.000864433717831981</t>
+          <t>-0.0027506112469438348 +/- 0.0011993531094345047</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.00042787286063565854 +/- 0.001268981631541972</t>
+          <t>6.112469437650204e-05 +/- 0.000576649213450876</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.001375305623471912 +/- 0.0012912365632199107</t>
+          <t>-0.0038814180929095943 +/- 0.0011997424466008999</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>9.168704156482521e-05 +/- 0.0005123182950562249</t>
+          <t>-0.0009779951100244988 +/- 0.0004054553533441803</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0015586797066015068 +/- 0.0019590917494544655</t>
+          <t>0.0013447432762835666 +/- 0.001231628464523819</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0018031784841075927 +/- 0.0011390369898278848</t>
+          <t>0.0036063569682151186 +/- 0.001091721949846669</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.0026283618581906644 +/- 0.0009086839087603146</t>
+          <t>-0.0015281173594132503 +/- 0.0007851609155663431</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.016045232273838594 +/- 0.0017409810964090615</t>
+          <t>-0.005592909535452384 +/- 0.0007975543001650144</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.00030562347188259895 +/- 0.0004533128659593788</t>
+          <t>0.0002750611246943313 +/- 0.0004822657040971617</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.00021393643031779596 +/- 0.0005302369062621649</t>
+          <t>-0.0012224938875305847 +/- 0.00038658651102302225</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.010544009779951059 +/- 0.0016070680715323759</t>
+          <t>-0.0006723716381418443 +/- 0.0014256606099866298</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.00696821515892414 +/- 0.001604450458240432</t>
+          <t>0.0017114914425427562 +/- 0.0013817426106915937</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0004889975550122605 +/- 0.0007993090972262868</t>
+          <t>-0.0010696821515892684 +/- 0.00041569286395890323</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.0007946210268948373 +/- 0.0006293172457816036</t>
+          <t>-0.0007640586797066362 +/- 0.0003131708669302938</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.003331295843520743 +/- 0.0018862193305879658</t>
+          <t>-0.00198655256723721 +/- 0.001730217586151354</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.009443765281173544 +/- 0.0014364303178484093</t>
+          <t>-0.004920537897310573 +/- 0.0009112500926574297</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.0009168704156478858 +/- 0.0003347937393063353</t>
+          <t>-0.0022921760391198644 +/- 0.0010520730121062786</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.001864303178484139 +/- 0.0009803798858401725</t>
+          <t>0.0016809290953544887 +/- 0.0006730658785313099</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.003178484107579427 +/- 0.0013544327509877848</t>
+          <t>-0.004462102689486625 +/- 0.00137496599990244</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.00357579462102684 +/- 0.0010502958604791872</t>
+          <t>-0.0017420537897310906 +/- 0.0007975543001650411</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.0055623471882640056 +/- 0.0013095528903195844</t>
+          <t>-0.0016503667481663098 +/- 0.001523219534764946</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.005073349633251778 +/- 0.0020510955666946675</t>
+          <t>0.006876528117359349 +/- 0.0014416230336272218</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0012836185819070423 +/- 0.0010831323439284364</t>
+          <t>-0.003636919315403486 +/- 0.0009803798858401829</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.005440097799511057 +/- 0.001532999535939431</t>
+          <t>-0.0008251833740831715 +/- 0.0013255041835086446</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.00024449877750615245 +/- 0.0004491729357181884</t>
+          <t>-0.0010696821515892795 +/- 0.0006868033329536766</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.003331295843520743 +/- 0.0008799621056777528</t>
+          <t>-0.002720048899755556 +/- 0.0009708056341240159</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0004278728606357363 +/- 0.001697242466615511</t>
+          <t>-0.0016809290953545663 +/- 0.0005676704040649985</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.0007640586797065696 +/- 0.0013198546993697525</t>
+          <t>-0.001955990220048964 +/- 0.0011451707821024096</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.00128361858190712 +/- 0.001150054261749807</t>
+          <t>-0.0013141809290953877 +/- 0.0010413646110880926</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.00021393643031790698 +/- 0.0005123182950562348</t>
+          <t>-0.0005501222493887847 +/- 0.0007707530692492925</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9.168704156483631e-05 +/- 0.00043329605375177225</t>
+          <t>-0.0009779951100244988 +/- 0.0005432881673175755</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00036161856864913534</t>
+          <t>-6.112469437654643e-05 +/- 0.0001833740831295838</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0008557457212714281 +/- 0.0016503667481662647</t>
+          <t>-0.0013141809290953877 +/- 0.001110805736270563</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.0014364303178483917 +/- 0.0010232682788987402</t>
+          <t>-0.0019559902200489533 +/- 0.0008223486581340896</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.0005501222493887181 +/- 0.0006081830300162718</t>
+          <t>-0.0008557457212714281 +/- 0.0004889975550122327</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-0.00015281173594128283 +/- 0.0011537033061232774</t>
+          <t>-0.0008251833740831715 +/- 0.0008541068834035561</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.00042787286063565854 +/- 0.0010951389283110615</t>
+          <t>-0.005806845965770224 +/- 0.000579879766534548</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.00015281173594126063 +/- 0.0003925804577831629</t>
+          <t>-0.001528117359413228 +/- 0.0005957698254773226</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.00042787286063572516 +/- 0.0012980905000975057</t>
+          <t>-0.0008251833740831604 +/- 0.0011108057362705656</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.0023533007334962885 +/- 0.001311334838198359</t>
+          <t>-0.0014364303178484583 +/- 0.0011520829355116838</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.004064792176039067 +/- 0.003465964212365976</t>
+          <t>-0.002811735941320348 +/- 0.0014897380937596556</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.00290342298288504 +/- 0.0008453127558642759</t>
+          <t>-0.0018337408312958825 +/- 0.0009950379337469344</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-0.0004278728606356474 +/- 0.00024449877750612193</t>
+          <t>6.112469437650204e-05 +/- 0.00018337408312956162</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.001222493887530518 +/- 0.000796968509193491</t>
+          <t>-0.0013141809290953988 +/- 0.0007975543001650432</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.0019254278728605856 +/- 0.000512318295056232</t>
+          <t>-0.0006112469437653089 +/- 0.0008751724366305904</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.001222493887530518 +/- 0.0005798797665345305</t>
+          <t>-0.0012530562347188745 +/- 0.0005012597636569947</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.003636919315403375 +/- 0.0014622095004774565</t>
+          <t>-0.0024449877750611915 +/- 0.0012301107455683514</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.001161369193154005 +/- 0.0012209648139020915</t>
+          <t>-0.003575794621026951 +/- 0.0014532388053751695</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.0013753056234718452 +/- 0.0010870060662456478</t>
+          <t>-0.0007334963325183908 +/- 0.0014606116314607029</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>-0.00015281173594129395 +/- 0.0003131708669302993</t>
+          <t>-0.0011919315403423393 +/- 0.00044183472783621437</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.00027506112469440904 +/- 0.00039731051344743697</t>
+          <t>-0.0016503667481662988 +/- 0.0005150458296562753</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>3.056234718830097e-05 +/- 0.0005870835181020553</t>
+          <t>-0.0010696821515892795 +/- 0.0005509705494290787</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.0006112469437652313 +/- 0.0005114058841895401</t>
+          <t>0.00033618581907086665 +/- 0.0006758357086643006</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.00030562347188261007 +/- 0.0014909915547250015</t>
+          <t>-0.001711491442542834 +/- 0.0011693842585396694</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.00012224938875308178 +/- 0.00041456784737929164</t>
+          <t>-0.00027506112469440904 +/- 0.0002139364303178737</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0025366748166258833 +/- 0.0010591518001933625</t>
+          <t>-0.00198655256723721 +/- 0.000700271347028707</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.007610024449877706 +/- 0.0011225163613818353</t>
+          <t>-0.0004278728606357474 +/- 0.0008109107066883489</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.00012224938875307067 +/- 0.0003667481662591658</t>
+          <t>-0.00027506112469440904 +/- 0.0002139364303178737</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.00015281173594137166 +/- 0.0010067034897310774</t>
+          <t>-0.0016809290953545663 +/- 0.0008229163825083436</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.002139364303178526 +/- 0.0012148292734933898</t>
+          <t>-0.00012224938875308178 +/- 0.0012391891768162133</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0013447432762836331 +/- 0.0010951389283110583</t>
+          <t>-0.0006418092909535877 +/- 0.0011308068459657847</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.000678265998230665 +/- 0.0019784574600671743</t>
+          <t>0.014007667354762643 +/- 0.0018428192037709347</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0007962253022706812 +/- 0.0013645220054567234</t>
+          <t>0.007755824240637033 +/- 0.001869989839278992</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.007873783544677137 +/- 0.0017398997345915576</t>
+          <t>-0.005042760247714506 +/- 0.0023718694742079554</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0010026540843408593 +/- 0.0015106161574598555</t>
+          <t>0.00017693895606021303 +/- 0.0017654532052015053</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.0027720436449425456 +/- 0.0009619290138779122</t>
+          <t>-0.012267767620171 +/- 0.0013590939099737817</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.0032438808611029656 +/- 0.0019292748137771775</t>
+          <t>0.008964907107048115 +/- 0.002693762842033444</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.0007372456502507063 +/- 0.0004800595870274207</t>
+          <t>0.00017693895606020195 +/- 0.00032838480464937006</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0067236803302859974 +/- 0.001249756419959708</t>
+          <t>0.007932763196697178 +/- 0.0015850610026985337</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.020967266293128804 +/- 0.0016230124335968226</t>
+          <t>0.02527278089059278 +/- 0.0021389782135993597</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.030168092008257097 +/- 0.002299639246815918</t>
+          <t>0.03352993217340024 +/- 0.003521658180625664</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.00026540843409018634 +/- 0.0008283439637386164</t>
+          <t>-0.004511943379534022 +/- 0.0019872292054062637</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.009230315541138368 +/- 0.0019068313960869231</t>
+          <t>-0.005868475375995252 +/- 0.0013478495879712682</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.0017104099085815893 +/- 0.0020968904552794107</t>
+          <t>8.846947803010652e-05 +/- 0.0018930998343502253</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.006900619286346166 +/- 0.0016109112690943898</t>
+          <t>0.011029194927749975 +/- 0.0018519986397059949</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.010645827189619627 +/- 0.0018671974188471567</t>
+          <t>-0.007578885284576764 +/- 0.0018133245814972694</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.0026540843409024405 +/- 0.0010043872819773592</t>
+          <t>-0.0013860218224711952 +/- 0.0015269352363314185</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.0017988793866116736 +/- 0.0011829059935199952</t>
+          <t>-0.0012385726924210693 +/- 0.0016408643754931976</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.8979652019997e-05 +/- 0.0012072833671753882</t>
+          <t>0.005337658507814836 +/- 0.0005963948220629977</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.0019758183426718313 +/- 0.0024568759688400107</t>
+          <t>0.009879091713358934 +/- 0.0015562695136489009</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.0005308168681804504 +/- 0.0001769389560601686</t>
+          <t>0.0005308168681804948 +/- 0.0003683278088114655</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0118254202300206 +/- 0.0009274069710124616</t>
+          <t>0.01654379239162492 +/- 0.0013985143852998168</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.004629902683574216 +/- 0.0021951605301028135</t>
+          <t>0.0017693895606016308 +/- 0.0017595321604454584</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0004718372161603646 +/- 0.0014638364666459186</t>
+          <t>0.003037452079032765 +/- 0.0020003147015171413</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.8979652019997e-05 +/- 0.0013692936321137187</t>
+          <t>0.000648776172220622 +/- 0.001297552344441191</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0006487761722205442 +/- 0.0010112903685923127</t>
+          <t>0.002123267472721957 +/- 0.0019905086441387573</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0007667354762606494 +/- 0.0006352302927908616</t>
+          <t>0.00023591860808024333 +/- 0.0008925240902637245</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0028900029489825397 +/- 0.0013306416010237052</t>
+          <t>0.005721026245945194 +/- 0.0026937628420334574</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.003420819817163123 +/- 0.0010567073351323347</t>
+          <t>0.005308168681804814 +/- 0.0011942469319561368</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.0007077558242406856 +/- 0.0013844523260755752</t>
+          <t>-0.0009141846063107862 +/- 0.0014712438434994232</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0114125626658803 +/- 0.0008552049542907796</t>
+          <t>-0.005367148333824801 +/- 0.001738649716659814</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.00035387791212038167 +/- 0.0009306832107378172</t>
+          <t>0.0019463285166617995 +/- 0.0009344134189180304</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.00029489826010031805 +/- 0.00047550915649062747</t>
+          <t>0.000530816868180517 +/- 0.0005405574396881084</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.016160424653494588 +/- 0.0014554954502215517</t>
+          <t>0.00038336773813039125 +/- 0.0021185520561087415</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.005986434680035446 +/- 0.0013581337587342418</t>
+          <t>0.00519020937776471 +/- 0.0014578834673321377</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.003243880861102977 +/- 0.00039564753361836884</t>
+          <t>0.0012090828664111264 +/- 0.0007512674257067175</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.003715718077263286 +/- 0.000970927610330536</t>
+          <t>0.0018283692126217054 +/- 0.0006433920445081588</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0019168386906516677 +/- 0.0017656994845087106</t>
+          <t>0.004777351813624342 +/- 0.001950791555121353</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.003922146859333575 +/- 0.001865333482850895</t>
+          <t>-0.0090238867590681 +/- 0.0023039840736802995</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.00011795930404008281 +/- 0.0005469547918310762</t>
+          <t>0.00044234739015042157 +/- 0.0006627014171113085</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.0012090828664110375 +/- 0.0018008121074340347</t>
+          <t>0.009908581539368955 +/- 0.0017154868265701908</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.00566204659392514 +/- 0.002452447406227281</t>
+          <t>0.00035387791212035944 +/- 0.0012840779154867253</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.00032438808611026106 +/- 0.0009996137573977213</t>
+          <t>0.0027425538189325025 +/- 0.0014865329591422546</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.008375110586847478 +/- 0.0016429829875770083</t>
+          <t>-0.0026835741669123726 +/- 0.002605973059288165</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.0017988793866115737 +/- 0.0012817053265762662</t>
+          <t>0.008611029194927799 +/- 0.0019463285166617555</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.0014450014744913585 +/- 0.0006521186784870755</t>
+          <t>0.0011501032143910628 +/- 0.0015905380784620362</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.008994396933058157 +/- 0.000934878648430986</t>
+          <t>0.00035387791212035944 +/- 0.0013042373569741048</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.0030374520790327764 +/- 0.00039674503235249703</t>
+          <t>-0.0003833677381303247 +/- 0.0006600716392096554</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.009407254497198514 +/- 0.0007277477251107684</t>
+          <t>-0.0010321439103509022 +/- 0.0010236835716726266</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.016307873783544723 +/- 0.0012375190361756017</t>
+          <t>0.010321439103509333 +/- 0.002438935196477161</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.012828074314361592 +/- 0.0010815170050658943</t>
+          <t>-0.016101445001474434 +/- 0.0020096402285344536</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.0007372456502507174 +/- 0.001550671403731648</t>
+          <t>-0.006635210852255935 +/- 0.0010488598787247762</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.00011795930404004951 +/- 0.0007934900647050386</t>
+          <t>0.00020642878207021153 +/- 0.00037418394398259857</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.004158065467413774 +/- 0.0007396010736646694</t>
+          <t>-0.0011206133883809644 +/- 0.0007553080787299131</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.0020642878207019376 +/- 0.000618583809006292</t>
+          <t>-0.0008552049542907225 +/- 0.0007396010736646463</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.0064877617222059095 +/- 0.0012015068585941363</t>
+          <t>-0.007195517546446428 +/- 0.0015503909676313822</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.010409908581539317 +/- 0.002366730784692811</t>
+          <t>-0.0020642878207018044 +/- 0.002183044001571424</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,147 +1616,147 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.00380418755529347 +/- 0.0007740728250313502</t>
+          <t>-0.0005603066941904711 +/- 0.0007277477251107526</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.004305514597463933 +/- 0.0013526800284493796</t>
+          <t>0.004865821291654415 +/- 0.0013005648523267334</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.0021822471247420093 +/- 0.0017654532052015063</t>
+          <t>0.000530816868180517 +/- 0.0016355558388513295</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.002270716602772116 +/- 0.0008851861409497747</t>
+          <t>0.0009141846063108527 +/- 0.0007962253022707156</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.009259805367148377 +/- 0.0011360283269984015</t>
+          <t>0.0011795930404011167 +/- 0.000978066880081219</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.011176644057800101 +/- 0.0014353398435432514</t>
+          <t>-0.005986434680035346 +/- 0.001915931096523824</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.008522559716897726 +/- 0.0011225518319477592</t>
+          <t>0.007785314066647053 +/- 0.0018044303793309693</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.002123267472721968 +/- 0.0011329621180948737</t>
+          <t>0.0058094957239752665 +/- 0.0006859158566566145</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.00035387791212028176 +/- 0.0001769389560601686</t>
+          <t>-0.00020642878207014493 +/- 0.00013513935992199742</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.009702152757298688 +/- 0.0012047595526874376</t>
+          <t>-0.003184901209082813 +/- 0.001490914144472377</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.0012385726924210472 +/- 0.000669880076178159</t>
+          <t>0.004570923031554153 +/- 0.0011740506775225182</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.0019168386906517898 +/- 0.0005786321695767835</t>
+          <t>0.0028310232969626092 +/- 0.0006072326830425731</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.02291359480979055 +/- 0.001911386661527433</t>
+          <t>0.02270716602772046 +/- 0.0010130087901691308</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.004452963727514048 +/- 0.0009641865363769922</t>
+          <t>0.002742553818932525 +/- 0.0014865329591422644</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.007401946328516618 +/- 0.0010587627880280868</t>
+          <t>0.006222353288115634 +/- 0.0010911235623709988</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-0.0012090828664111596 +/- 0.00027820646216620507</t>
+          <t>0.00026540843409027514 +/- 0.00035996920128968985</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0015924506045415065 +/- 0.0008567289322520786</t>
+          <t>-0.0010026540843408704 +/- 0.0008767955616230301</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.00262459451489232 +/- 0.000869324858329904</t>
+          <t>0.0010911235623709992 +/- 0.0009605719536952349</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>5.897965202006361e-05 +/- 0.00011795930404012722</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.0007077558242406523 +/- 0.00044136330130037366</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.012651135358301414 +/- 0.0018056348587250685</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0005308168681804504 +/- 0.0003176151463954118</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>-0.00014744913005018123 +/- 0.000997872268692954</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.000678265998230576 +/- 0.00037418394398258545</t>
+          <t>0.0006487761722205998 +/- 0.0005564129243324548</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.007755824240637044 +/- 0.0008949567033614593</t>
+          <t>0.002270716602772094 +/- 0.0009330163385170373</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.009171335889118315 +/- 0.0007396010736646463</t>
+          <t>0.005042760247714595 +/- 0.001512054702836235</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.0011206133883809532 +/- 0.0004530313033246124</t>
+          <t>-0.0002654084340902085 +/- 0.0007277477251107775</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.0015334709525214318 +/- 0.0008627979261767996</t>
+          <t>0.00566204659392513 +/- 0.0013629277509043234</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.0026835741669123726 +/- 0.0009459755194541538</t>
+          <t>0.009790622235328861 +/- 0.0011632605675798227</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.005897965202005351 +/- 0.0006724714981416504</t>
+          <t>0.002093777646711925 +/- 0.0009551244317724451</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.0016572950577094403 +/- 0.0011477194098647857</t>
+          <t>0.0012429712932820135 +/- 0.000979754090396363</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.005031074282332093 +/- 0.002071618822136727</t>
+          <t>-0.010861201538916832 +/- 0.001949874686005228</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.00026635099141755216 +/- 0.0016071232888293038</t>
+          <t>-0.0035217519976324385 +/- 0.0016972419010286824</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.0009174311926605783 +/- 0.0025335773573038813</t>
+          <t>-0.003462562888428544 +/- 0.0020420242675347833</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.002012429712932784 +/- 0.0010977944356905045</t>
+          <t>-0.0031370227878070424 +/- 0.00120722569129159</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.002989050014797323 +/- 0.001883153390936119</t>
+          <t>0.006481207457827753 +/- 0.0017279266738081962</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.9594554601952706e-05 +/- 0.0002458308334690123</t>
+          <t>-5.918910920390541e-05 +/- 0.00025799934557801685</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0007694584196507703 +/- 0.0012569849412012379</t>
+          <t>-0.0011837821840781193 +/- 0.001537778165938626</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.01772713820656996 +/- 0.0035499898760114976</t>
+          <t>0.012192956496004737 +/- 0.003145387453231478</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.02450429121041725 +/- 0.003284328949157764</t>
+          <t>0.02406037289138797 +/- 0.003006579536684537</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.004942290618526158 +/- 0.0013500437677368734</t>
+          <t>0.0027818881325835875 +/- 0.001550257573685577</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.00041432376442732675 +/- 0.0010009786638228951</t>
+          <t>-0.002426753477360155 +/- 0.0010654039656703388</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-5.918910920392762e-05 +/- 0.0010319973823120947</t>
+          <t>-0.007517016868896132 +/- 0.0016855911057588944</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.009144717372003518 +/- 0.0020735204564194558</t>
+          <t>0.0129032258064516 +/- 0.0013048480429149573</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.005208641609943709 +/- 0.002025444052354988</t>
+          <t>0.007161882213672688 +/- 0.0017598187330356352</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.0011245930748742029 +/- 0.0010571512932519341</t>
+          <t>-0.0037881029890500127 +/- 0.002221760802500565</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0015981059485055127 +/- 0.0012845536794442777</t>
+          <t>-0.003403373779224628 +/- 0.0015277785734407147</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.0005918910920390986 +/- 0.0010752235646395586</t>
+          <t>-0.00029594554601952705 +/- 0.0006207806144836534</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.001302160402485919 +/- 0.0011245930748742029</t>
+          <t>-0.0010654039656702973 +/- 0.0006510802012429595</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.0010949985202723055 +/- 0.0004781146617758202</t>
+          <t>-0.00032554010062147977 +/- 0.00015937155392525617</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00032554010062146865 +/- 0.0019606252826341267</t>
+          <t>0.0030778336786031367 +/- 0.0014328166246712463</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0003847292098253741 +/- 0.0008981350047643428</t>
+          <t>0.002426753477360155 +/- 0.0013868451629310587</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.00011837821840784412 +/- 0.0015726937266157502</t>
+          <t>-0.001538916839301563 +/- 0.001553643651779427</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0025155371411660797 +/- 0.0015104824096093335</t>
+          <t>0.00041432376442733786 +/- 0.0011323543338093308</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0016277005031074764 +/- 0.0009748250424386515</t>
+          <t>-0.003284995560816806 +/- 0.0014404372327479246</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-5.918910920391651e-05 +/- 0.0005091639696385253</t>
+          <t>0.00038472920982538514 +/- 0.0006624157823497777</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.0056525599289730995 +/- 0.0030853653834245313</t>
+          <t>0.002456348031962119 +/- 0.0024370176828695136</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.003018644569399276 +/- 0.0013805153938668902</t>
+          <t>0.001834862385321079 +/- 0.0011057438113210658</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.00014797277300976353 +/- 0.0007968577696262809</t>
+          <t>0.001213376738680072 +/- 0.001409707648868242</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0017756732761171623 +/- 0.0008474590744762411</t>
+          <t>0.0011837821840781193 +/- 0.0012130157757868688</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.918910920390541e-05 +/- 0.0004143237644273379</t>
+          <t>0.00014797277300976353 +/- 0.0005806870929372072</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.9594554601952706e-05 +/- 0.0007059402451539714</t>
+          <t>-0.00011837821840781082 +/- 0.0009743757107519402</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.0031370227878069977 +/- 0.0011167778789057847</t>
+          <t>0.0024859425865640496 +/- 0.0014749850008141073</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.0044983722994969225 +/- 0.0010488336872843463</t>
+          <t>0.003107428233205101 +/- 0.0013185362184046012</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.00014797277300976353 +/- 0.0003563656282566463</t>
+          <t>-5.918910920390541e-05 +/- 0.00041432376442733786</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0008878366380585812 +/- 0.0007368984668830131</t>
+          <t>0.0011541876294761555 +/- 0.0006270973690564282</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.00011837821840778861 +/- 0.0016855911057588786</t>
+          <t>-0.00204202426753477 +/- 0.0020308420792302857</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0035217519976323717 +/- 0.0008312857002182826</t>
+          <t>0.001834862385321079 +/- 0.0009974725981860123</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.0009174311926605783 +/- 0.0006676835852429164</t>
+          <t>-0.0008878366380585812 +/- 0.0010079542092883158</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.00479431784551646 +/- 0.0012749724314020747</t>
+          <t>-0.002811482687185551 +/- 0.001271188611714403</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0021899970405445 +/- 0.0009283449033061756</t>
+          <t>0.0008286475288546757 +/- 0.0009974725981859965</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0034921574430304635 +/- 0.0018847805064327629</t>
+          <t>0.0007990529742527563 +/- 0.002234535860433581</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.002545131695767933 +/- 0.0013248315646995554</t>
+          <t>-0.002012429712932795 +/- 0.0014364795619427775</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.0005622965374370903 +/- 0.0015460145470978213</t>
+          <t>0.001716484166913279 +/- 0.001630657273034141</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0025451316957679436 +/- 0.0011245930748742302</t>
+          <t>0.0007990529742527231 +/- 0.0009548544424327545</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.0003847292098254185 +/- 0.0010341169109000486</t>
+          <t>-2.9594554601952706e-05 +/- 0.001286257106368768</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.00014797277300976353 +/- 0.0005496944546021418</t>
+          <t>-0.00026635099141757433 +/- 0.000503107428233196</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.00032554010062146865 +/- 0.000994394650275912</t>
+          <t>-0.0021012133767386643 +/- 0.0010459068983174012</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.002308375258952311 +/- 0.0016090295612983653</t>
+          <t>0.004143237644273457 +/- 0.0019361263372354074</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.878366380584701e-05 +/- 0.0012061369560411245</t>
+          <t>-0.001420538620893741 +/- 0.001354900638326087</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0009174311926605338 +/- 0.001054247595771326</t>
+          <t>0.005563776265167209 +/- 0.002010688103162219</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.001686889612311304 +/- 0.000675508269340818</t>
+          <t>-0.001006214856466392 +/- 0.0007392717370107471</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.00026635099141757433 +/- 0.0005202247952425755</t>
+          <t>-0.0005622965374371014 +/- 0.0006544345779075343</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.0034921574430305303 +/- 0.0005091639696385009</t>
+          <t>-0.000503107428233196 +/- 0.00043995468325890014</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.004675939627108572 +/- 0.0013994188123749073</t>
+          <t>0.004409588635691031 +/- 0.0019426745702605872</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.0010654039656702863 +/- 0.001451038848432221</t>
+          <t>0.004143237644273457 +/- 0.0014737969337660663</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.00014797277300976353 +/- 0.0005496944546021419</t>
+          <t>-0.0004439183190292906 +/- 0.0005496944546021418</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.0001479727730097302 +/- 0.0014693331266417914</t>
+          <t>-0.0018940514945249953 +/- 0.0010353865454001822</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.00239715892275818 +/- 0.0016125638029979542</t>
+          <t>-0.0021012133767386643 +/- 0.001141981733150338</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>-0.0006510802012429928 +/- 0.0007102693104469084</t>
+          <t>0.0015685113939034935 +/- 0.0006214856466410069</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.0012725658478839664 +/- 0.0010837427300148105</t>
+          <t>0.0007694584196507703 +/- 0.001084954292975616</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0002663509914175632 +/- 0.0012725658478839918</t>
+          <t>0.0015981059485054793 +/- 0.0017367742824647874</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.0025747262503699854 +/- 0.0010674571646564904</t>
+          <t>-0.002515537141166024 +/- 0.0012642799268004871</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-0.0013317549570879494 +/- 0.0007279297943917932</t>
+          <t>-0.003580941106836355 +/- 0.0014343439853273451</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-0.00014797277300976353 +/- 0.0002728483118464848</t>
+          <t>2.9594554601952706e-05 +/- 0.00020716188221366893</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0008878366380585701 +/- 0.0011073268383468315</t>
+          <t>-0.0011837821840781193 +/- 0.001234486748423453</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0038768866528558045 +/- 0.0006806747558449122</t>
+          <t>0.0012725658478839664 +/- 0.0007009600048728498</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.00038472920982538514 +/- 0.00039815401145526687</t>
+          <t>-0.00017756732761171624 +/- 0.0004987362990929983</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.0012725658478839551 +/- 0.0013172070484917331</t>
+          <t>0.0018644569399230426 +/- 0.0018484162734095548</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.000503107428233196 +/- 0.0006214856466410069</t>
+          <t>0.002752293577981646 +/- 0.0009908652881197829</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.0010358094110684223 +/- 0.0005955789226842007</t>
+          <t>-0.0012725658478839885 +/- 0.0016373573475730154</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>2.9594554601952706e-05 +/- 8.878366380585811e-05</t>
+          <t>0.0 +/- 0.00013235087170759095</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.0006510802012430039 +/- 0.0005889242007142227</t>
+          <t>2.9594554601952706e-05 +/- 0.0006676835852428691</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.001272565847884033 +/- 0.0005302300345418793</t>
+          <t>-0.00011837821840781082 +/- 0.00035513465522343243</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.00026635099141759656 +/- 0.0006409117439392888</t>
+          <t>-0.00017756732761171624 +/- 0.0006774503191630298</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-0.00017756732761171624 +/- 0.0006235959605121365</t>
+          <t>0.0018644569399230205 +/- 0.0007374925004070368</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-0.00011837821840782192 +/- 0.0006643961030081092</t>
+          <t>-0.0005327019828351487 +/- 0.0004546401744817088</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0010654039656702973 +/- 0.0005488972178452523</t>
+          <t>0.002633915359573824 +/- 0.0012234404621837677</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.002485942586564116 +/- 0.0013248315646995868</t>
+          <t>0.00029594554601952705 +/- 0.0013561928662195197</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.002219591595146564 +/- 0.0007157967814411131</t>
+          <t>0.0005918910920390541 +/- 0.0006207806144836534</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0016277005031073988 +/- 0.0005955789226841593</t>
+          <t>-0.0008878366380586034 +/- 0.0014498311587944354</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.0027818881325836543 +/- 0.000899596576121384</t>
+          <t>0.003166617342409006 +/- 0.0018719579284840005</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0005031074282332404 +/- 0.0007946565008640521</t>
+          <t>5.918910920390541e-05 +/- 0.0008658620206171961</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0003249630723781372 +/- 0.001147587864080055</t>
+          <t>-0.0013884785819793133 +/- 0.0010066011838936917</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.0015361890694239211 +/- 0.0013264368874826313</t>
+          <t>0.0002954209748892156 +/- 0.000758950226213593</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.00227474150664696 +/- 0.000886755156266089</t>
+          <t>-0.003426883308714912 +/- 0.0017537160507717518</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.0001477104874446078 +/- 0.0008063423376044968</t>
+          <t>0.002067946824224509 +/- 0.001441218424537714</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0015361890694239211 +/- 0.000721214512007896</t>
+          <t>0.002067946824224509 +/- 0.0009057435578585413</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.002127031019202352 +/- 0.0019317911638725826</t>
+          <t>0.002954209748892156 +/- 0.0013473269425100527</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.00017725258493352935 +/- 0.0003783234409118355</t>
+          <t>0.0009158050221565684 +/- 0.000360607256003948</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.001477104874446078 +/- 0.0011816838995568624</t>
+          <t>0.0003840472673559803 +/- 0.0007595249708822673</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.02779911373707531 +/- 0.003798084448368557</t>
+          <t>0.03491875923190544 +/- 0.003871705743079696</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.02443131462333824 +/- 0.0036351187834188473</t>
+          <t>0.02138847858197932 +/- 0.002451104107851277</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.00322008862629245 +/- 0.0008607859547612046</t>
+          <t>-0.003279172821270293 +/- 0.0011996419795714532</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0008862629246676468 +/- 0.0015743471308093538</t>
+          <t>-0.0031019202363367637 +/- 0.0011307331881243447</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.000265878877400294 +/- 0.0008708657591127679</t>
+          <t>-0.003426883308714901 +/- 0.0014900467016742602</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.007090103397341197 +/- 0.0016711533971912745</t>
+          <t>-0.014091580502215695 +/- 0.002345017385224937</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.007828655834564213 +/- 0.0021024760234750954</t>
+          <t>0.008064992614475585 +/- 0.001471481170506612</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.002688330871491862 +/- 0.0003840472673559803</t>
+          <t>-0.0036632200886262734 +/- 0.001322483266505127</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.000880830222503722</t>
+          <t>0.0015952732644017643 +/- 0.0012050858525477716</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.002481536189069411 +/- 0.00104196112783151</t>
+          <t>-0.0005908419497784312 +/- 0.0007236306477941404</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.000858247506430362</t>
+          <t>0.00360413589364843 +/- 0.0006965923853797067</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.00047267355982274497 +/- 0.0003012714631369429</t>
+          <t>-0.0001477104874446078 +/- 0.0003794751131067965</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0036632200886262734 +/- 0.0012266197631921173</t>
+          <t>-0.0023633677991137247 +/- 0.0017124226583384772</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0008271787296898036 +/- 0.0010469746024619946</t>
+          <t>0.0039290989660265676 +/- 0.0006997175351448715</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0008567208271787252 +/- 0.0008298122248264736</t>
+          <t>0.0023633677991137247 +/- 0.000803631935523508</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0003840472673559803 +/- 0.0006612416332525635</t>
+          <t>0.0011225997045790192 +/- 0.001736713554705937</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0030428360413589208 +/- 0.0005125362355361117</t>
+          <t>0.006292466765140292 +/- 0.00128804900186656</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0001477104874446078 +/- 0.00023817600438104898</t>
+          <t>0.00017725258493352935 +/- 0.0003783234409118355</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0039290989660265676 +/- 0.0015966403683156975</t>
+          <t>0.009010339734121076 +/- 0.00138091531964788</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.005701624815361861 +/- 0.0016237407484385492</t>
+          <t>-0.0002067946824224509 +/- 0.0009439613180898301</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0003840472673559803 +/- 0.0009346701340949065</t>
+          <t>0.0005022156573116666 +/- 0.0011136234460839389</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.00023633677991137249 +/- 0.001038605366691099</t>
+          <t>0.00927621861152137 +/- 0.0007948965463559019</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00034954681140913357</t>
+          <t>0.0003840472673559803 +/- 0.0005125362355361117</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.00017725258493352935 +/- 0.0003545051698670587</t>
+          <t>-0.0012112259970457838 +/- 0.0004061366937922437</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,272 +2381,272 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.0026587887740029403 +/- 0.0006736634712550263</t>
+          <t>0.005997045790251077 +/- 0.0008464726015890297</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.0054062038404726455 +/- 0.0013015297354156913</t>
+          <t>0.0019497784342688228 +/- 0.0011978218571765547</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.0003545051698670587 +/- 0.000368980679373611</t>
+          <t>5.908419497784312e-05 +/- 0.0002210728145804385</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.000265878877400294 +/- 0.0003084285527004578</t>
+          <t>0.0005908419497784312 +/- 0.000803631935523508</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.004431314623338234 +/- 0.0014412184245377138</t>
+          <t>0.0015952732644017643 +/- 0.0010830311834459832</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0005612998522895096 +/- 0.0004470530561424366</t>
+          <t>-0.0002067946824224509 +/- 0.0009802457916122287</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.001063515509601176 +/- 0.0004614623146769048</t>
+          <t>-0.0017725258493352936 +/- 0.0010894587246431716</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.0020974889217134306 +/- 0.0014009932881984418</t>
+          <t>0.002215657311669117 +/- 0.0012198418210967487</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.001802067946824215 +/- 0.000900428399062221</t>
+          <t>0.002127031019202352 +/- 0.001251971645519467</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0003249630723781372 +/- 0.0007641073652217132</t>
+          <t>-0.0011816838995568624 +/- 0.0008459569313604891</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0018316100443131367 +/- 0.000995704552221721</t>
+          <t>-0.0015361890694239211 +/- 0.001427834088460208</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.0003545051698670587 +/- 0.0010635155096011763</t>
+          <t>0.0001477104874446078 +/- 0.0016514534545788613</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.0003249630723781372 +/- 0.0007169666823935914</t>
+          <t>0.004224519940915783 +/- 0.0017923558419045715</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.002127031019202352 +/- 0.0007793740595729897</t>
+          <t>-0.0005908419497784312 +/- 0.0015236392269692832</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-5.908419497784312e-05 +/- 0.0004135893648449018</t>
+          <t>0.000265878877400294 +/- 0.00033553372796456396</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0018906942392909799 +/- 0.0009904315872520013</t>
+          <t>0.004785819793205292 +/- 0.00047267355982274497</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.00023633677991137249 +/- 0.0015897930927118039</t>
+          <t>-0.003545051698670587 +/- 0.0007816104316291216</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.004697193500738528 +/- 0.0010930576070900975</t>
+          <t>0.0009453471196454899 +/- 0.0012021855213811344</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.0011456850475429963</t>
+          <t>-0.002392909896602646 +/- 0.0008298122248264737</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.0002954209748892156 +/- 0.0002288321031732583</t>
+          <t>0.00017725258493352935 +/- 0.000442145629160877</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.0002954209748892156 +/- 0.0002288321031732583</t>
+          <t>0.00017725258493352935 +/- 0.0005937888107013789</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>-8.862629246676468e-05 +/- 0.0001353788979307479</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.0010930576070900977 +/- 0.0010237945909106862</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-0.006410635155096022 +/- 0.0010898591873381002</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.0049335302806499 +/- 0.0009346701340949065</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>0.0013293943870014702 +/- 0.0009640867871244097</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0003840472673559803 +/- 0.00037484719469570025</t>
+          <t>0.0015066469719349994 +/- 0.0009290508238414361</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0004431314623338234 +/- 0.0008788463681325518</t>
+          <t>0.002895125553914313 +/- 0.0013132118623865733</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.0006794682422451958 +/- 0.000886755156266089</t>
+          <t>-0.0022451994091580384 +/- 0.0008582475064303619</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0005022156573116666 +/- 0.00029689440535068945</t>
+          <t>0.0 +/- 0.0005758814974776316</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.0006794682422451958 +/- 0.0005915800411964751</t>
+          <t>0.0069128508124076445 +/- 0.0013158675008165422</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.0003545051698670587 +/- 0.0008229476086962509</t>
+          <t>-0.0004431314623338234 +/- 0.0010994265326988656</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.0004135893648449018 +/- 0.0006083090186698344</t>
+          <t>0.0018316100443131367 +/- 0.0014460547415681363</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.0013293943870014702 +/- 0.0006231912292386669</t>
+          <t>-0.00360413589364843 +/- 0.0011802058703360753</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.908419497784312e-05 +/- 0.00011816838995568624</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.002156573116691274 +/- 0.0007932479516748882</t>
+          <t>-0.000531757754800588 +/- 0.0011875776214027578</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0006203840472673528 +/- 0.0006259858227597335</t>
+          <t>0.0005022156573116666 +/- 0.000953161938251202</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.0007680945347119606 +/- 0.0005150840701377431</t>
+          <t>0.0002067946824224509 +/- 0.0008668479025773196</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.003751846381093038 +/- 0.0017579409804208876</t>
+          <t>-0.006262924667651415 +/- 0.001299852289512592</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0002067946824224509 +/- 0.0008255946004420707</t>
+          <t>0.00017725258493352935 +/- 0.000981580367848512</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.0035155096011816656 +/- 0.001068836189963099</t>
+          <t>-0.005169867060561295 +/- 0.0014244683546518692</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00018684062984746606</t>
+          <t>-2.954209748892156e-05 +/- 8.862629246676468e-05</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.000265878877400294 +/- 0.00042708514903399956</t>
+          <t>2.954209748892156e-05 +/- 0.0005674851613677531</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.00023633677991137249 +/- 0.00017725258493352935</t>
+          <t>5.908419497784312e-05 +/- 0.0004538343130202995</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>5.908419497784312e-05 +/- 0.00011816838995568624</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0004431314623338234 +/- 0.0003302906909157722</t>
+          <t>-0.0005612998522895096 +/- 0.00042708514903399956</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.0004135893648449018 +/- 0.0004007285071270448</t>
+          <t>-0.003870014771048724 +/- 0.0007754448891229908</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0001477104874446078 +/- 0.0001477104874446078</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.0002954209748892156 +/- 0.0004381801174059453</t>
+          <t>0.0012407680945347055 +/- 0.0007090103397341174</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.0006794682422451958</t>
+          <t>-0.000738552437223039 +/- 0.0012551046254799345</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-8.862629246676468e-05 +/- 0.0008041747467542764</t>
+          <t>-0.0015066469719349994 +/- 0.0009196090053928095</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.00017725258493352935 +/- 0.0004007285071270448</t>
+          <t>-0.0006203840472673528 +/- 0.0004661664353931881</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0009453471196454899 +/- 0.000525151811953651</t>
+          <t>-0.002688330871491862 +/- 0.0009476522855152353</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.0035155096011816656 +/- 0.0011089113370235369</t>
+          <t>-0.000265878877400294 +/- 0.0012283972163244716</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0006499261447562743 +/- 0.00041358936484490186</t>
+          <t>-0.00011816838995568624 +/- 0.0010079008631747057</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.006483126110124393 +/- 0.0017734832209295515</t>
+          <t>-0.004470100651272934 +/- 0.0012238026411245941</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0027531083481350583 +/- 0.0016956783293806575</t>
+          <t>-0.0027531083481349694 +/- 0.0009081031172396692</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.001983422143280089 +/- 0.0016538161898713385</t>
+          <t>-0.004677323860272331 +/- 0.0017997257730693545</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0024570751924215097 +/- 0.0006885555565194119</t>
+          <t>-0.005654233274126686 +/- 0.001385042932538745</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.0015985790408526213 +/- 0.0013252237587684649</t>
+          <t>-0.0031675547661337957 +/- 0.001527083525935918</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0012729425695677365 +/- 0.0008786750787244527</t>
+          <t>-0.002545885139135562 +/- 0.001649305894278746</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00014801657785666887 +/- 0.0002729290839932572</t>
+          <t>0.0005032563647128785 +/- 0.00032563647128479187</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.0001184132622854217 +/- 0.0010012749866955316</t>
+          <t>-0.0024866785079928786 +/- 0.0007394905859559906</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.010627590290112444 +/- 0.002733942724607206</t>
+          <t>-0.003848431024274701 +/- 0.002199428729544921</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.015393724097098816 +/- 0.0022815688416811856</t>
+          <t>0.0073416222616933145 +/- 0.0026603483645542955</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.010005920663114332 +/- 0.0019312618626761494</t>
+          <t>-0.007726465364120782 +/- 0.0014649902938612999</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.001835405565423298 +/- 0.0013025458851391337</t>
+          <t>-0.0027827116637063275 +/- 0.000727543263910285</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.001480165778567255 +/- 0.0012061307748646307</t>
+          <t>-0.001657785671995271 +/- 0.001396071772948668</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.006986382474837238 +/- 0.0030079066420084107</t>
+          <t>-0.009177027827116635 +/- 0.0028084171049452817</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.0076376554174066745 +/- 0.00279528043436659</t>
+          <t>0.0032267613972764898 +/- 0.0021892447477186838</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.000651272942569514 +/- 0.000769686204854923</t>
+          <t>-0.000858496151568966 +/- 0.0007541586265753031</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.0012137359384251645 +/- 0.0013976402171833055</t>
+          <t>-0.0035523978685612747 +/- 0.001191510467584261</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.008496151568975773 +/- 0.0011237568322144632</t>
+          <t>-0.00876258140911781 +/- 0.0008900708335330419</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0011841326228538174 +/- 0.0009995229731281274</t>
+          <t>2.9603315571358203e-05 +/- 0.0008625697030392727</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.00013239005195379546</t>
+          <t>-0.0001184132622853773 +/- 0.0002368265245707546</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.007844878626406215 +/- 0.0016495715471586704</t>
+          <t>-0.006749555950266417 +/- 0.0009153123051355861</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.0071047957371225936 +/- 0.0018487264648899973</t>
+          <t>-0.006719952634695092 +/- 0.001583431512174828</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.003611604499703924 +/- 0.0008456398376012826</t>
+          <t>0.000355239786856143 +/- 0.0012822029501307292</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0004144464179987595 +/- 0.0008497750203912</t>
+          <t>0.0025754884547069313 +/- 0.0007948917455356627</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.004647720544701051 +/- 0.0011001127398497324</t>
+          <t>-0.00011841326228536619 +/- 0.0011249259917110752</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0002072232089994408 +/- 0.0006492513972605416</t>
+          <t>-0.000562462995855506 +/- 0.0006678812417216312</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.00926583777383061 +/- 0.002628034235638384</t>
+          <t>0.003256364712847848 +/- 0.002050977865682503</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.022972172883362986 +/- 0.0027427435931084497</t>
+          <t>-0.015571343990526931 +/- 0.002168127107590342</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.01811722912966256 +/- 0.0018382681700722197</t>
+          <t>-0.006039076376554176 +/- 0.001214818503770478</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.001953818827708664 +/- 0.001109235878933977</t>
+          <t>0.003937240970988742 +/- 0.0006885555565194133</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-0.0001480165778567688 +/- 0.0004997614865640555</t>
+          <t>-0.0006216696269982003 +/- 0.00027927712054636833</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.9206631142727506e-05 +/- 0.00039273236120253676</t>
+          <t>0.0010657193605683956 +/- 0.0005328596802841948</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.0014209591474245498 +/- 0.0013159331421487867</t>
+          <t>-0.003818827708703354 +/- 0.001079202257759512</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.02089994079336891 +/- 0.0019511257611940914</t>
+          <t>-0.008940201302545848 +/- 0.0026767683967927353</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.0008584961515689215 +/- 0.00048553047563221793</t>
+          <t>-0.0004144464179988039 +/- 0.00035523978685611887</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-5.551115123125783e-17 +/- 0.000945454080679204</t>
+          <t>-0.00014801657785670219 +/- 0.0007160086810211805</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.004351687388987513 +/- 0.0016162976547920216</t>
+          <t>0.004203670811130855 +/- 0.001309256624481683</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0012729425695677365 +/- 0.0015385182309279107</t>
+          <t>-0.0057430432208407265 +/- 0.0012362707529793343</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.001865008880994734 +/- 0.0005778336677307042</t>
+          <t>0.00112492599171109 +/- 0.0004144464179988055</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.005150976909413796 +/- 0.000818251921911493</t>
+          <t>0.0008584961515689882 +/- 0.001346544158146173</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.00929544108940208 +/- 0.0010099894676869284</t>
+          <t>-0.002220248667850799 +/- 0.0017970456140646773</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>8.88099467139858e-05 +/- 0.0014138488971296107</t>
+          <t>-0.00423327412670218 +/- 0.0014261917667786588</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0038188277087033095 +/- 0.0013001889435167251</t>
+          <t>-0.004026050917702762 +/- 0.001545054866867948</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.001480165778567255 +/- 0.0011076546438051962</t>
+          <t>-0.000888099467140313 +/- 0.0016105944948176713</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.003670811130846707 +/- 0.0014754216452785227</t>
+          <t>-0.001332149200710464 +/- 0.0010694133728945216</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.002812314979277741 +/- 0.0014697680979640542</t>
+          <t>-0.000976909413854332 +/- 0.0014981149708561427</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.0005032563647129118 +/- 0.000496241995685048</t>
+          <t>0.0007696862048549802 +/- 0.0003791074148864832</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.0017465956187092569 +/- 0.0009769094138543366</t>
+          <t>0.000355239786856143 +/- 0.001167737295637417</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.006009473060982773 +/- 0.0016643804377585137</t>
+          <t>0.004114860864416814 +/- 0.002018459909263569</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0030787448194198206 +/- 0.0024129880251408825</t>
+          <t>0.005062166962699832 +/- 0.0014589960367497456</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.004588513913558278 +/- 0.0017172474851714923</t>
+          <t>0.003966844286560123 +/- 0.000938009444508859</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.001036116044997093 +/- 0.0003564711242981601</t>
+          <t>-0.0008584961515689549 +/- 0.0005530355740754636</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.00047365304914146476 +/- 0.0006095695761389401</t>
+          <t>-0.0007696862048549247 +/- 0.0005950192789295731</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0008288928359976744 +/- 0.0003927323612025351</t>
+          <t>-0.002101835405565422 +/- 0.00044797945383131757</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.0034635879218472 +/- 0.0012352069890482484</t>
+          <t>0.0036412078152753048 +/- 0.0012632675129278798</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00603907637655412 +/- 0.001791917815325235</t>
+          <t>0.00683836589698047 +/- 0.0015464722186629904</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,147 +2951,147 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.0007992895204263495 +/- 0.00047825619956788667</t>
+          <t>-0.0005920663114268754 +/- 0.0006619502597690319</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.0007992895204262274 +/- 0.0008058411834704711</t>
+          <t>0.0015393724097098938 +/- 0.0017653110143132774</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.0012433392539963894 +/- 0.002088240626234257</t>
+          <t>-0.002279455298993471 +/- 0.0015944621680870454</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.0005328596802842367 +/- 0.0007347349701593212</t>
+          <t>0.0006216696269982225 +/- 0.0006131532024040395</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.004884547069271816 +/- 0.0014875481973239838</t>
+          <t>-0.0032859680284191618 +/- 0.0005203787990304133</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.009502664298401364 +/- 0.0014529770505397194</t>
+          <t>-0.007696862048549413 +/- 0.0017860394468914608</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.002309058614564885 +/- 0.0010981194192416649</t>
+          <t>0.0013913558318531583 +/- 0.0011845026064974888</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.006453522794552935 +/- 0.0011973800127979054</t>
+          <t>0.000799289520426305 +/- 0.0015667399197630998</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-0.0002960331557134932 +/- 0.0003744556139927075</t>
+          <t>0.0006216696269982558 +/- 0.00027927712054636247</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.000532859680284159 +/- 0.0009889457127584397</t>
+          <t>0.0006216696269982225 +/- 0.0013850429325387382</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.0033155713439905975 +/- 0.0011450017528604921</t>
+          <t>0.004381290704558916 +/- 0.0010065127294256898</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.00011841326228533289 +/- 0.000938009444508873</t>
+          <t>-0.0014209591474245054 +/- 0.0005740295864317837</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.010035523978685557 +/- 0.0016292584849990437</t>
+          <t>-0.005565423327412678 +/- 0.0016365038438230207</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.0020426287744226834 +/- 0.0013136002209789093</t>
+          <t>0.0002368265245707768 +/- 0.0008031178191977845</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.0009473060982829407 +/- 0.001631140001652565</t>
+          <t>0.0033747779751332253 +/- 0.0014147783475842019</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.00032563647128474037 +/- 0.0002459036075464019</t>
+          <t>-0.0001184132622853884 +/- 0.00019636618060128762</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.0008880994671402797 +/- 0.0008979130188338157</t>
+          <t>-0.0017465956187092569 +/- 0.0006272830106695387</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.001006512729425757 +/- 0.0008288928359976498</t>
+          <t>0.0010361160449970709 +/- 0.0008080132660719952</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
+          <t>0.0002072232089994297 +/- 0.00013565943442736298</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>-8.880994671401909e-05 +/- 0.001059534053769876</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>-0.0024866785079928565 +/- 0.0008801698488643379</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>-0.0005328596802842478 +/- 0.0007347349701593311</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>-0.00538780343398465 +/- 0.0010237783579508828</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.00014801657785666887 +/- 0.00019858507793068077</t>
+          <t>0.0002072232089994186 +/- 0.0005466603112083907</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.00011841326228544391 +/- 0.0010690035574462764</t>
+          <t>-0.003996447602131447 +/- 0.0010694133728945355</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.001006512729425635 +/- 0.001170735342408824</t>
+          <t>-0.0023978685612788377 +/- 0.0010121563645517527</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.000621669626998178 +/- 0.0008209250813417376</t>
+          <t>-0.0001776198934280715 +/- 0.0007628240809191954</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0002368265245706991 +/- 0.0009619938904246088</t>
+          <t>0.0014801657785671995 +/- 0.0007129422485963524</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.001006512729425646 +/- 0.0010356930541465799</t>
+          <t>0.0004736530491415092 +/- 0.0017067537365778073</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.0007104795737122082 +/- 0.0012362707529793408</t>
+          <t>-0.0013617525162818 +/- 0.0012075830701226023</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.0022876841115638037 +/- 0.0012381539495542964</t>
+          <t>-0.003415857098088404 +/- 0.0010896483015176246</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.0027890943277969595 +/- 0.0010805979097190039</t>
+          <t>-0.00598558445628331 +/- 0.0011251220978386737</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.000282043246631114 +/- 0.0018878465035197676</t>
+          <t>-0.00141021623315577 +/- 0.0017121640087305232</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.002632403635224101 +/- 0.0010783234430639611</t>
+          <t>0.0038859291758069348 +/- 0.0015429061266175052</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.0023190222500783842 +/- 0.0011908492635537306</t>
+          <t>0.0010028204324662893 +/- 0.0019103416677064564</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0028204324663115288 +/- 0.001789295195690395</t>
+          <t>0.0013475399561265976 +/- 0.0010303530067548375</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.000344719523660264 +/- 0.0003271797715107999</t>
+          <t>0.0002507051081165557 +/- 0.0004387339392040121</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.001911626449388948 +/- 0.001512369603511562</t>
+          <t>-0.004387339392040124 +/- 0.0011471642254918869</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0034471952366029067 +/- 0.002193669696020046</t>
+          <t>-0.00012535255405828893 +/- 0.0017061306911709585</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.011908492635537426 +/- 0.0035620864276735427</t>
+          <t>0.0042933249764963936 +/- 0.002443772073316429</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.0012848636790975033 +/- 0.0012648346017305244</t>
+          <t>-0.003039799435913526 +/- 0.0015227239878729394</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.0017235976183014312 +/- 0.0019683245061036876</t>
+          <t>-0.0010654967094954615 +/- 0.00044759814657117735</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.0015669069257286616 +/- 0.0014631924199221334</t>
+          <t>0.0019116264493888812 +/- 0.0014993260688067262</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.004324663115011007 +/- 0.001037476988859095</t>
+          <t>-0.007489815104982767 +/- 0.001383499846734213</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.004794735192729526 +/- 0.0019116264493889157</t>
+          <t>0.0017235976183014757 +/- 0.0011994772302729366</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.0032591664055155677 +/- 0.0013236422489465867</t>
+          <t>0.00219366969602004 +/- 0.0015731620680678301</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.001410216233155781 +/- 0.001239739294569267</t>
+          <t>-0.0005640864932623168 +/- 0.0007255303605634777</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.00012535255405823342 +/- 0.0009317498431412431</t>
+          <t>-0.0047947351927295715 +/- 0.0009301674760047526</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.001347539956126642 +/- 0.0013225288527740047</t>
+          <t>-0.0005954246317768863 +/- 0.0012413226148754856</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0004387339392039613 +/- 0.0005463991154547995</t>
+          <t>-9.401441554370837e-05 +/- 0.0001436093918820255</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.0003133813851457501 +/- 0.0013515423787431927</t>
+          <t>-0.005233469131933588 +/- 0.0013877524177677728</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>9.401441554368617e-05 +/- 0.0013150821221157905</t>
+          <t>-0.00012535255405831113 +/- 0.0014237313308180066</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.00021936696960204172 +/- 0.0010013503797349009</t>
+          <t>0.002287684111563748 +/- 0.0011216252064038413</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0005954246317768974 +/- 0.001272575399827445</t>
+          <t>0.0016609213412723145 +/- 0.0006581009088060136</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0010341585709809254 +/- 0.0009088060169225924</t>
+          <t>0.00015669069257283618 +/- 0.0015809461931218368</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0009714822939516976 +/- 0.0005508742034235888</t>
+          <t>-0.0005640864932623391 +/- 0.00041574738832408817</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.0020996552804763645 +/- 0.0008414742451957086</t>
+          <t>0.006518332811031013 +/- 0.001455115859134294</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.0034158570980884263 +/- 0.0008913483330195952</t>
+          <t>0.003196490128486351 +/- 0.0009168748880180409</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.006706361642118508 +/- 0.0009211493861923358</t>
+          <t>-0.004512691946098424 +/- 0.0013745980695368885</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.002036979003447248 +/- 0.0015368473626122378</t>
+          <t>-0.0007834534628643252 +/- 0.0013090942384334312</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.0006267627702914669 +/- 0.000485488354272318</t>
+          <t>-0.0002820432466311584 +/- 0.0004945074847401917</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.267627702909451e-05 +/- 0.0005570789355885603</t>
+          <t>-0.0009401441554371837 +/- 0.0007007420800688706</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.00031338138514567235 +/- 0.0011299126529188354</t>
+          <t>0.003133813851457212 +/- 0.0014360939188203666</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.008931369476653128 +/- 0.0014513990820318714</t>
+          <t>0.002538389219680337 +/- 0.0014594962108674344</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.00034471952366031954 +/- 0.0007983540710032558</t>
+          <t>-0.0020369790034472147 +/- 0.000321120362455648</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.000282043246631114 +/- 0.0005327483547477324</t>
+          <t>0.0015982450642431534 +/- 0.0008576579243750605</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.00031338138514567235 +/- 0.0011725657746079294</t>
+          <t>0.0037919147602632265 +/- 0.0008461297398934622</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0033218426825446954 +/- 0.0011908492635537475</t>
+          <t>-0.00040739580068943626 +/- 0.001529159874491481</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.0002193669696019529 +/- 0.0007014424721278235</t>
+          <t>0.000971482293951742 +/- 0.0007605553807277646</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.0020056408649326563 +/- 0.0007442395541860053</t>
+          <t>0.0016609213412723035 +/- 0.0009714822939517416</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.00018802883108740565 +/- 0.0014028849442556898</t>
+          <t>0.005797555625195849 +/- 0.0021903094647454067</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0073644625509244445 +/- 0.0016538106928184063</t>
+          <t>0.0042306486994672324 +/- 0.0013314099521308442</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.0074898151049828 +/- 0.0015571617986593071</t>
+          <t>-0.004011281729865257 +/- 0.0020299761505110227</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0003447195236602529 +/- 0.0006490854019808332</t>
+          <t>-0.0015669069257286173 +/- 0.0013295646152050435</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0002820432466311029 +/- 0.0006180847045852552</t>
+          <t>-0.004450015669069274 +/- 0.000938052619686365</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.00517079285490446 +/- 0.0017574521959022186</t>
+          <t>-0.002789094327796948 +/- 0.0007475312091430006</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.000407395800689403 +/- 0.0005253229274283922</t>
+          <t>-0.0001566906925728806 +/- 0.0003773611588465231</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.0034471952366029847 +/- 0.0015669069257286063</t>
+          <t>0.0012848636790974365 +/- 0.0013692292243781621</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.00031338138514568347 +/- 0.0015352489769872605</t>
+          <t>-0.0014728925101848978 +/- 0.0013591506388092476</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.0017862738953306478 +/- 0.000971482293951736</t>
+          <t>-0.0044186775305547045 +/- 0.001813555160918871</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.0011281729865246337 +/- 0.0018550483969851173</t>
+          <t>-0.0076151676590410665 +/- 0.0016466693394446346</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.0004700720777186196 +/- 0.0006901509102333017</t>
+          <t>0.0028204324663114845 +/- 0.0005427924812187049</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.001566906925728584 +/- 0.000610892782501331</t>
+          <t>0.0004700720777185641 +/- 0.0003773611588465185</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0005954246317768197 +/- 0.0005508742034236102</t>
+          <t>0.001316201817612017 +/- 0.0005912868149205034</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.004230648699467288 +/- 0.0016890646165104142</t>
+          <t>-0.010216233155750576 +/- 0.0017346728302222421</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.005421497963021038 +/- 0.0021024598079247437</t>
+          <t>-0.0035098715136321124 +/- 0.001703826664878482</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.0012535255405829338 +/- 0.0007415957108241448</t>
+          <t>-0.002256345973049212 +/- 0.0005014102162331335</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.002632403635224034 +/- 0.001131649644955666</t>
+          <t>-0.002413036665622059 +/- 0.0011039746132126963</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.005264807270448158 +/- 0.0020154102401521248</t>
+          <t>-0.0016922594797869172 +/- 0.001096387068914818</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0008774678784079781 +/- 0.0005014102162331571</t>
+          <t>0.0008774678784079892 +/- 0.00041574738832409814</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0009088060169226364 +/- 0.0008913483330196181</t>
+          <t>-0.00250705108116579 +/- 0.0011123935662362063</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.0016101827112084126</t>
+          <t>-0.005640864932623002 +/- 0.0010202958693888691</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.00307113757442804 +/- 0.0008501823858508428</t>
+          <t>-0.0026950799122532287 +/- 0.0013162018176120472</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.003071137574428129 +/- 0.0011539926442821664</t>
+          <t>-0.004230648699467265 +/- 0.0014032349217949164</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0.0006267627702914002 +/- 0.00028029683202755116</t>
+          <t>-0.0002193669696020084 +/- 0.0002820432466311572</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.0032591664055155456 +/- 0.0012472421649722615</t>
+          <t>-0.0005327483547477363 +/- 0.0009301674760047695</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.000501410216233189 +/- 0.0009830389935041209</t>
+          <t>-0.00159824506424322 +/- 0.0013548082934012732</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0009714822939516865 +/- 0.0009653977938420121</t>
+          <t>0.0027577561892823455 +/- 0.0005912868149205034</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.0011281729865246447 +/- 0.0011990677824950812</t>
+          <t>0.002663741773738626 +/- 0.0014648694318420824</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0022563459730491563 +/- 0.0012597775770756357</t>
+          <t>0.000971482293951742 +/- 0.0009653977938420212</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.0024130366656220925 +/- 0.0009195487778828677</t>
+          <t>-0.0065810090880601855 +/- 0.0012690978835046408</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>9.401441554367507e-05 +/- 0.00031494439426892426</t>
+          <t>-6.267627702915002e-05 +/- 0.0003070497953974458</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0005327483547476808 +/- 0.0007682639092529913</t>
+          <t>0.00018802883108740565 +/- 0.00040132398855735764</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.0017549357568161007 +/- 0.0005812358818862866</t>
+          <t>0.0007834534628642809 +/- 0.0003773611588465277</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.0001566906925728917 +/- 0.0007448990488251193</t>
+          <t>-0.0011281729865246337 +/- 0.0009104255121487854</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0006894390473205392 +/- 0.0008951962931423282</t>
+          <t>0.00018802883108741674 +/- 0.001293623781921061</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.00031338138514567235 +/- 0.0008524895336092269</t>
+          <t>-0.0007207771858351753 +/- 0.0007682639092529592</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.003008461297398968 +/- 0.0011908492635537469</t>
+          <t>-0.003697900344719518 +/- 0.00144835098819071</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.0012221874020682754 +/- 0.000760555380727771</t>
+          <t>-0.0038545910372923984 +/- 0.0011978385994118816</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0012221874020683532 +/- 0.000532748354747722</t>
+          <t>-0.0017235976183014867 +/- 0.0006306678720619812</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.0003760576621748446 +/- 0.001128172986524614</t>
+          <t>-0.0027577561892823455 +/- 0.0011539926442821675</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.003541209652146693 +/- 0.0017840733722958746</t>
+          <t>-0.004606706361642132 +/- 0.0008057010424432651</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.000814791601378917 +/- 0.0007309247126098796</t>
+          <t>0.004293324976496382 +/- 0.0011729844733445816</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.002152886115444641 +/- 0.0012898612548264865</t>
+          <t>0.003900156006240252 +/- 0.0009989273381330206</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00046801872074880846 +/- 0.0017937325868087025</t>
+          <t>0.009297971918876735 +/- 0.002807418877803933</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0013104524180967303 +/- 0.0011489518027782708</t>
+          <t>0.0012168486739469464 +/- 0.0019951728273008558</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.36037441497728e-05 +/- 0.002425081753737674</t>
+          <t>-0.004336973478939155 +/- 0.0013416536661466352</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0048361934477379135 +/- 0.0007674492278470418</t>
+          <t>0.005709828393135741 +/- 0.0018930185724951674</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.004399375975039 +/- 0.0014664586583463253</t>
+          <t>0.001747269890795633 +/- 0.0017605910739052668</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.0007800312012480215 +/- 0.0004007872879458601</t>
+          <t>0.00040561622464896363 +/- 0.00028081123244929864</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0024960998439937598 +/- 0.001034828327724001</t>
+          <t>-0.0021528861154446076 +/- 0.0015186388173027174</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.014321372854914204 +/- 0.0020386141933128993</t>
+          <t>0.015850234009360354 +/- 0.0030115266176633294</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.015600624024960996 +/- 0.0041604264089318745</t>
+          <t>0.01850234009360373 +/- 0.004132369433006706</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.005865834633385336 +/- 0.001796715138706763</t>
+          <t>-0.004305772230889238 +/- 0.0012464888833346869</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.004149765990639631 +/- 0.0009048361934477245</t>
+          <t>0.0019656786271450843 +/- 0.0019834277785101824</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0004368174726989249 +/- 0.001929438356785076</t>
+          <t>0.011482059282371282 +/- 0.0017749095355167478</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.01672386895475818 +/- 0.001798881161360335</t>
+          <t>0.007675507020280803 +/- 0.002867121374766958</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.005210608424336971 +/- 0.0014504386020804394</t>
+          <t>0.015163806552262082 +/- 0.002121684867394694</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.0041809672386895255 +/- 0.0014311818959350723</t>
+          <t>0.012636505460218406 +/- 0.0012264114824981763</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0022464898595943917 +/- 0.0014216269266639102</t>
+          <t>-0.0012792511700468023 +/- 0.002052890377484688</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0004368174726989249 +/- 0.0012100292935828625</t>
+          <t>0.0025585023400936046 +/- 0.0013149021844434188</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.0033697347893915652 +/- 0.001386964790695349</t>
+          <t>-0.001060842433697362 +/- 0.0018522086838884072</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.0007488299531981157 +/- 0.0003181915453099934</t>
+          <t>-0.00018720748829953449 +/- 0.00042323432031982696</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.006989079563182532 +/- 0.001339838412080113</t>
+          <t>0.008205928237129479 +/- 0.001560374383781601</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.0022464898595943804 +/- 0.001322285185673483</t>
+          <t>-0.01391575663026522 +/- 0.001152336056949721</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.003993759750390002 +/- 0.0012620123816634186</t>
+          <t>0.002028081123244929 +/- 0.0013108238088985894</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.002464898595943843 +/- 0.001319705833544871</t>
+          <t>0.0072386895475819 +/- 0.0015835978209609572</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.006177847113884571 +/- 0.0009443211201511267</t>
+          <t>0.004118564742589703 +/- 0.0013369288789783725</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.00015600624024960651 +/- 0.00037571277936946946</t>
+          <t>-0.0009048361934477333 +/- 0.0009091296277275061</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.011107644305772236 +/- 0.0019243861397952257</t>
+          <t>0.010296411856474253 +/- 0.002982943751068233</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.0030889235569422913 +/- 0.0015998057713939636</t>
+          <t>-0.006333853354134167 +/- 0.0011678606722129855</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.005366614664586577 +/- 0.0013869647906953474</t>
+          <t>-0.00474258970358814 +/- 0.0016140427028240333</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.008143525741029644 +/- 0.0016179584602139384</t>
+          <t>-0.013478939157566306 +/- 0.0018658241981561279</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0003744149765990357 +/- 0.00038970346323857346</t>
+          <t>-0.0005616224648986145 +/- 0.0009128698183043728</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00018720748829952337 +/- 0.00042323432031982376</t>
+          <t>-0.0005304212168486755 +/- 0.0005928237129485104</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.004336973478939144 +/- 0.0018639971333845734</t>
+          <t>-0.0063338533541341556 +/- 0.0012868387286927676</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.0006864274570982709 +/- 0.0012464888833346823</t>
+          <t>-0.007737909516380681 +/- 0.0005887039707991637</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.00308892355694228 +/- 0.0006310061908317037</t>
+          <t>0.000655226209048354 +/- 0.0010758776692397331</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0010608424336973287 +/- 0.0007917989104804676</t>
+          <t>-0.001060842433697362 +/- 0.0006424730197183538</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0012480499219968632 +/- 0.0013163820973309916</t>
+          <t>0.0007800312012480548 +/- 0.0018045546010510172</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.0009672386895475671 +/- 0.0011544461778471272</t>
+          <t>-0.007925117004680193 +/- 0.001820399643783457</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.000967238689547556 +/- 0.0006757069525025763</t>
+          <t>0.0015912636505460154 +/- 0.0007948667209271123</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.001809672386895489 +/- 0.0010139205497205729</t>
+          <t>0.0006864274570982487 +/- 0.0014753934998486076</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.0025585023400935937 +/- 0.00163799123225043</t>
+          <t>-0.0069266770670826875 +/- 0.001238654180423055</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0006864274570982709 +/- 0.001922361535194926</t>
+          <t>-0.007519500780031196 +/- 0.001985390111692094</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.004212168486739465 +/- 0.0006871362104694079</t>
+          <t>-0.007269890795631828 +/- 0.0014164816802266747</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.0015912636505460154 +/- 0.0018163843466867894</t>
+          <t>0.0039001560062402628 +/- 0.0017217322510229484</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0018096723868954666 +/- 0.0006050146467914514</t>
+          <t>0.0018408736349453947 +/- 0.0013915196955368305</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.001716068642745705 +/- 0.001404056162246502</t>
+          <t>0.0014664586583463257 +/- 0.0017206010207753033</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.0005616224648985702 +/- 0.0004992199687987545</t>
+          <t>0.0007800312012480326 +/- 0.0007546575115412103</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.0010920436817472789 +/- 0.0014315219652985462</t>
+          <t>-0.0013728549141965641 +/- 0.0016224648985959608</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.0011544461778471016 +/- 0.0012792511700468183</t>
+          <t>0.004087363494539797 +/- 0.0019256504367188142</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.0021840873634945248 +/- 0.0018193297643823087</t>
+          <t>0.0014664586583463368 +/- 0.0009365573179284711</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.011107644305772236 +/- 0.001126706401576766</t>
+          <t>-0.009079563182527306 +/- 0.0008539115247053898</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0007800312012480326 +/- 0.0005449063711879302</t>
+          <t>0.000280811232449274 +/- 0.0007310686124093441</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0017784711388455499 +/- 0.0005928237129485186</t>
+          <t>-0.00021840873634947354 +/- 0.00044235403677870904</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>9.360374414975059e-05 +/- 0.00014298208096583733</t>
+          <t>0.0005304212168486643 +/- 0.0002436895374697904</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.00521060842433696 +/- 0.0010631341677005165</t>
+          <t>-0.0049921996879875195 +/- 0.0013163820973309576</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.002340093603744142 +/- 0.0015616216856464615</t>
+          <t>-0.007113884555382222 +/- 0.0015958454730164498</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,107 +3841,107 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.00031201248049922414 +/- 0.0011921980140120066</t>
+          <t>0.0006864274570982598 +/- 0.0005719283238634547</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.0013728549141965641 +/- 0.000839539722126266</t>
+          <t>-0.004180967238689548 +/- 0.0015613099535971037</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.001716068642745716 +/- 0.0007149104048293077</t>
+          <t>0.006427457098283929 +/- 0.0018626909899032075</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.0007176287051481988 +/- 0.0009969763063132641</t>
+          <t>-0.0008736349453978165 +/- 0.000823145457614528</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.00037441497659906897 +/- 0.0012542746485018246</t>
+          <t>-0.00071762870514821 +/- 0.0010446595346510444</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.010982839313572546 +/- 0.0012849460394367416</t>
+          <t>-0.00439937597503901 +/- 0.0016179584602139566</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.002527301092043688 +/- 0.0008652371060132428</t>
+          <t>-0.005148205928237148 +/- 0.001530134144803652</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.006333853354134167 +/- 0.001294381810464374</t>
+          <t>-0.00037441497659906897 +/- 0.0013441909034969121</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-9.360374414976169e-05 +/- 0.0003432137285491128</t>
+          <t>9.360374414976169e-05 +/- 0.00019978546762660653</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.006053042121684882 +/- 0.0007917989104804816</t>
+          <t>0.008237129485179396 +/- 0.0014037094389019774</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.005148205928237115 +/- 0.0009989273381330638</t>
+          <t>-0.0006240249609984483 +/- 0.0018876110405309638</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.001809672386895478 +/- 0.00043681747269891857</t>
+          <t>-0.0003432137285491632 +/- 0.0005993564028798254</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.016505460218408728 +/- 0.0015057633088316521</t>
+          <t>0.009516380655226208 +/- 0.0017497753376361678</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0018408736349454168 +/- 0.0009302996265757129</t>
+          <t>3.120124804990576e-05 +/- 0.0019557483861734537</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.0036817472698908007 +/- 0.0010790400290664876</t>
+          <t>-0.0015912636505460043 +/- 0.0021182407578775207</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002416838281564293</t>
+          <t>0.0006864274570982598 +/- 0.00030570854824128117</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.0029641185647425903 +/- 0.0011611727966258027</t>
+          <t>0.0003120124804992019 +/- 0.0005031050076941509</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.002808112324492984 +/- 0.0007383562911824845</t>
+          <t>-0.002152886115444619 +/- 0.0008189956161252236</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>6.240249609983373e-05 +/- 0.00012480499219966746</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.0006240249609984372 +/- 0.00046278929716665474</t>
+          <t>0.0007800312012480215 +/- 0.0004883767813572167</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.00015600624024961763 +/- 0.0011942377041500487</t>
+          <t>-0.004617784711388462 +/- 0.0013369288789783777</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.001716068642745716 +/- 0.0005267376916110614</t>
+          <t>-0.001060842433697362 +/- 0.0006574510922216875</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.005304212168486722 +/- 0.0013600308716195527</t>
+          <t>-0.0023400936037441646 +/- 0.002393564856662795</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.00486739469578783 +/- 0.0016043631990243351</t>
+          <t>0.0009360374414976502 +/- 0.001248049921996877</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.001310452418096697 +/- 0.000479322667573709</t>
+          <t>-0.0005304212168486866 +/- 0.0005590163141082152</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.004492979719188772 +/- 0.0019142417036103639</t>
+          <t>-0.0063650546021840945 +/- 0.0014447222343575894</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.018190327613104518 +/- 0.0015160724634329132</t>
+          <t>0.006271450858034322 +/- 0.0009509984807568272</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0003432137285491299 +/- 0.0009812284052116164</t>
+          <t>-0.0011232449297971959 +/- 0.000851056580155113</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.012024756852342989 +/- 0.0019540918896847306</t>
+          <t>0.006395520188623671 +/- 0.001305133499881197</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.013793103448275824 +/- 0.0016345917623179686</t>
+          <t>0.008664898320070757 +/- 0.0011949976382383332</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.017624521072796894 +/- 0.0019272363954343386</t>
+          <t>0.015826702033598615 +/- 0.0022831158746671773</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.006749189507810149 +/- 0.0013726060739398813</t>
+          <t>0.0049218980253463275 +/- 0.0017488362745825884</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.008871205422929495 +/- 0.0018332238774045311</t>
+          <t>0.003477748305334538 +/- 0.0013811228427774893</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.013822575891541377 +/- 0.0019834319314342803</t>
+          <t>0.002328323017978229 +/- 0.0020095365674896054</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0002063071028587826 +/- 0.00026525198938993384</t>
+          <t>-2.9472443265532446e-05 +/- 0.0001587139642538961</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.00872384320660179 +/- 0.002218082843763836</t>
+          <t>0.0019157088122605747 +/- 0.001358612504758774</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.04588859416445619 +/- 0.0030601707757431725</t>
+          <t>0.04538756262894197 +/- 0.0018732977992420513</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.04977895667550836 +/- 0.0037453202405866534</t>
+          <t>0.04087827880931334 +/- 0.003163451850688247</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.00014736221632766222 +/- 0.0014926563232656072</t>
+          <t>0.002446212791040403 +/- 0.0014856567239762562</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.006572354848216855 +/- 0.0012576827759122812</t>
+          <t>0.0056292366637194615 +/- 0.001137269754292651</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0166814028882994 +/- 0.0011043320952075068</t>
+          <t>0.014883583849101123 +/- 0.002206500086559966</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.003448275862068928 +/- 0.0023171039211318427</t>
+          <t>0.005806071323312722 +/- 0.0033449600135126278</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.02791040377247269 +/- 0.000941735650378452</t>
+          <t>0.017329796640141493 +/- 0.0010852904591524895</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.00185676392572951 +/- 0.0018360646185879724</t>
+          <t>0.00011788977306221859 +/- 0.0012860255955951432</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.009843796050692554 +/- 0.0014023433248889195</t>
+          <t>0.011022693781314496 +/- 0.0011353586963901191</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.0014441497200117447 +/- 0.0009636181977171766</t>
+          <t>0.0012967875036840825 +/- 0.0011580832716998792</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.006984969053934531 +/- 0.0017488362745825981</t>
+          <t>0.0012083701738874407 +/- 0.0017358743675363441</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00035366931918652257 +/- 0.0003174279285077468</t>
+          <t>2.9472443265576854e-05 +/- 0.0003347426080636866</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.011317418213969999 +/- 0.0024167403477748416</t>
+          <t>-0.003094606542882372 +/- 0.0025600341719102734</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.0008841732979664507 +/- 0.001455831303887823</t>
+          <t>-0.0036251105216622117 +/- 0.001635919727247617</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.002151488358384868 +/- 0.0008648040525270398</t>
+          <t>-0.0031535514294134593 +/- 0.0014914920045835472</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.002829354553492436 +/- 0.0010964382692448045</t>
+          <t>0.0003241968759210456 +/- 0.0014100646877578129</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0011199528440907435 +/- 0.0010020630710286067</t>
+          <t>0.003065134099616873 +/- 0.001104332095207502</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0020041261420571275 +/- 0.0006694852161273497</t>
+          <t>-0.001650456822870594 +/- 0.0009150707159599193</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.015944591806660736 +/- 0.0023073365783730817</t>
+          <t>0.009961685823754817 +/- 0.002045311119704986</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.009755378720896024 +/- 0.0020858912206567003</t>
+          <t>-0.0005894488653109154 +/- 0.0023056418762874096</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.00294724432655471 +/- 0.001200798631739658</t>
+          <t>-0.006189213085764767 +/- 0.0008939434652580803</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.00035366931918652257 +/- 0.0014183565476588087</t>
+          <t>-0.0041556145004420396 +/- 0.0012112421213106008</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0013262599469495372 +/- 0.0005630702379765108</t>
+          <t>-0.00011788977306215198 +/- 0.0008460182784796547</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.000943118184497449 +/- 0.0008419013767807614</t>
+          <t>0.0016504568228706384 +/- 0.0005923887781385712</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.841732979668615e-05 +/- 0.0018688875758901004</t>
+          <t>-0.0006778661951075571 +/- 0.001748836274582591</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0021809608016505 +/- 0.0014329791666540725</t>
+          <t>-0.004185086943707572 +/- 0.0018443251219760655</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.000383141762452055 +/- 0.000746182664377973</t>
+          <t>-0.0009136457412319166 +/- 0.0003597570178524626</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0010904804008252556 +/- 0.0009600057456470494</t>
+          <t>0.0006189213085765255 +/- 0.0009174407554537778</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.0054229295608605455 +/- 0.0017742312930494944</t>
+          <t>0.0002652519893899696 +/- 0.001082485568653511</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0010610079575596233 +/- 0.0007243268922749705</t>
+          <t>-0.003183023872679003 +/- 0.002019668930033797</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0016799292661361376 +/- 0.0013249494130851314</t>
+          <t>-0.000943118184497449 +/- 0.0007548628632399523</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.005098732684939544 +/- 0.0008130335528519669</t>
+          <t>-0.0028588269967580126 +/- 0.001103151622293716</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.002475685234306002 +/- 0.0009613620059121646</t>
+          <t>-0.0004420866489831754 +/- 0.0011953610250912778</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0027998821102268923 +/- 0.0013839501187001412</t>
+          <t>0.002652519893899241 +/- 0.0007685472920958098</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.002858826996757979 +/- 0.0013637176895089104</t>
+          <t>-0.002269378131447064 +/- 0.000995540569057143</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.015797229590332983 +/- 0.0018225316632761914</t>
+          <t>0.010521662245800234 +/- 0.00295915659238981</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.004686118479221879 +/- 0.0008278556973290919</t>
+          <t>0.0015915119363395624 +/- 0.0014510502357902813</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.008930150309460616 +/- 0.0014320696272627663</t>
+          <t>-0.0032714412024756447 +/- 0.0015508779389239967</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0009725906277631036 +/- 0.0006855115443332114</t>
+          <t>-0.0009431181844974712 +/- 0.000810358213077964</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-0.002122015915119402 +/- 0.001085290459152502</t>
+          <t>0.0006778661951075904 +/- 0.0017388741526672528</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.010433244916003493 +/- 0.0025530690041506298</t>
+          <t>0.007810197465369905 +/- 0.0011125603352889562</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.0029177718832891775 +/- 0.0022307738838981753</t>
+          <t>-0.0008252284114352859 +/- 0.0016609493431895565</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.00669024462127904 +/- 0.0012011602636200938</t>
+          <t>0.011229000884173335 +/- 0.001979047682192701</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.0007662835249041544 +/- 0.0005305039787798443</t>
+          <t>-0.0010904804008252 +/- 0.0007461826643779646</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.00014736221632769553 +/- 0.0009885357990714982</t>
+          <t>-0.0008841732979663619 +/- 0.000574523686696657</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-0.00011788977306221859 +/- 0.00023577954612439555</t>
+          <t>0.0005599764220454384 +/- 0.0001587139642538734</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.013203654582964897 +/- 0.002002391718415896</t>
+          <t>0.009725906277630435 +/- 0.002282925638790124</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.004214559386973127 +/- 0.0018026441123929343</t>
+          <t>0.0012083701738874407 +/- 0.0024814677111455034</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,147 +4286,147 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0007073386383731562 +/- 0.0004966784422738718</t>
+          <t>-0.00020630710285879372 +/- 0.0006727210262607317</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.0035956380783966567 +/- 0.0019849641309145666</t>
+          <t>0.0002947244326555132 +/- 0.0009320004892921784</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0.005039787798408424 +/- 0.001422331684292798</t>
+          <t>0.0036251105216622893 +/- 0.0011866090267726279</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.0010315355142940796 +/- 0.0008465314834273622</t>
+          <t>0.0009725906277630702 +/- 0.0005280422300963445</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.00020630710285888255 +/- 0.0012226624528553784</t>
+          <t>-0.0043029767167697686 +/- 0.0020170867824660962</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.0074565281461832725 +/- 0.0016830287692625161</t>
+          <t>-0.002092543471853792 +/- 0.0020052093950101908</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.00014736221632768442 +/- 0.0012659435069209961</t>
+          <t>-0.00020630710285879372 +/- 0.0016306013785585647</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.008399646330680754 +/- 0.001364991002288173</t>
+          <t>-0.000677866195107546 +/- 0.0009417356503784381</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-5.8944886531109296e-05 +/- 0.00011788977306221858</t>
+          <t>0.0004420866489832531 +/- 0.0003548952130501557</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.00232832301797814 +/- 0.00200087286442602</t>
+          <t>0.001473622163277366 +/- 0.0018358280580486137</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.0014736221632772883 +/- 0.0011261404759530071</t>
+          <t>-0.0013557323902151142 +/- 0.0011429837565378766</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.003035661656351274 +/- 0.0010382502183205733</t>
+          <t>-0.00014736221632770662 +/- 0.0009249840746522287</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.0038019451812554726 +/- 0.002421228929978287</t>
+          <t>0.016033009136457443 +/- 0.0015991346850870022</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.004627173592690881 +/- 0.0014680117188815025</t>
+          <t>-0.0010610079575596564 +/- 0.0011949976382383185</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.0002063071028587826 +/- 0.001357333208331213</t>
+          <t>-0.004420866489831976 +/- 0.0015143215536298409</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-0.0004126142057177096 +/- 0.00027011940435930654</t>
+          <t>-0.00017683465959325017 +/- 0.00023577954612437056</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.0006778661951075237 +/- 0.0008130335528519798</t>
+          <t>-0.00047155909224871895 +/- 0.0005775395797897428</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.0012673150604185612 +/- 0.001029849997621946</t>
+          <t>-0.0010315355142941018 +/- 0.0009155452146778076</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-2.9472443265554648e-05 +/- 8.841732979666395e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.00014736221632770662 +/- 0.0007600233986576917</t>
+          <t>0.000648393751842069 +/- 0.0006293591660495858</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0013262599469495596 +/- 0.0008866259331854548</t>
+          <t>8.841732979666394e-05 +/- 0.0016830287692625172</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.004244031830238759 +/- 0.0004209506883903877</t>
+          <t>0.00014736221632776213 +/- 0.00027172250095176923</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.0044798113763631405 +/- 0.0009845737157966566</t>
+          <t>-0.00041261420571762073 +/- 0.00042095068839038925</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0036840554081932985 +/- 0.0016892107139295338</t>
+          <t>-0.0016504568228706052 +/- 0.0011877065534694937</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.0034482758620690166 +/- 0.0006463811435149104</t>
+          <t>-0.005629236663719383 +/- 0.0012741506820640864</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.004656646035956435 +/- 0.0011399398529804792</t>
+          <t>-0.0054524020041261 +/- 0.0005313220270356738</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.0008841732979664507 +/- 0.0016672131592962997</t>
+          <t>0.00017683465959332788 +/- 0.0019109419484170122</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.005246094901267373 +/- 0.0012350325281318471</t>
+          <t>0.004420866489832043 +/- 0.0017386243682584914</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.005570291777188263 +/- 0.0008172958811589846</t>
+          <t>-0.0003831417624520772 +/- 0.0008944291721481752</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0010371650821088929 +/- 0.0013402135810559497</t>
+          <t>-0.007692307692307654 +/- 0.0008551323583783346</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.006626332469029117 +/- 0.0016092469079537818</t>
+          <t>-0.011264765197349424 +/- 0.0010181847909577842</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.014289830020167104 +/- 0.0015418136744753182</t>
+          <t>-0.02100259291270524 +/- 0.0012185702093089259</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.002131950446557185 +/- 0.001541813674475323</t>
+          <t>-0.0041486603284355715 +/- 0.0016660135171191123</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0027369634111207076 +/- 0.0013951368496460152</t>
+          <t>-0.007317775857101671 +/- 0.0011466291410044643</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0018438490348602454 +/- 0.001270262615099321</t>
+          <t>0.0032843560933448757 +/- 0.0013525433125099954</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0005762028233938122 +/- 0.0005153714727743765</t>
+          <t>-8.643042350905405e-05 +/- 0.00022501439573340218</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.0019878997407087318 +/- 0.0015485283376982704</t>
+          <t>-0.000374531835205949 +/- 0.0010936475307463261</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.0020167098818784424 +/- 0.0027962167809970485</t>
+          <t>-0.010400460962258684 +/- 0.002800517628782529</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.005387496398732372 +/- 0.0034259849235031004</t>
+          <t>-0.008268510515701478 +/- 0.00144079513109189</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.003630077787381181 +/- 0.0012438509446800888</t>
+          <t>-0.008095649668683336 +/- 0.0015908311947310132</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.008383751080380319 +/- 0.001081436149762229</t>
+          <t>-0.016162489196197016 +/- 0.0020713269337964413</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.012878133102852208 +/- 0.0018628825307205298</t>
+          <t>-0.009276865456640693 +/- 0.0022046818173101787</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.00786516853932585 +/- 0.0017431921068747655</t>
+          <t>-0.025352924229328676 +/- 0.00155681429975295</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.013339095361567266 +/- 0.00249519774384034</t>
+          <t>-0.004350331316623412 +/- 0.001985392930454639</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.002996254681647925 +/- 0.0009996745360355908</t>
+          <t>-0.002448861999423757 +/- 0.0015897873421286644</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.0012100259291270676 +/- 0.001214134687738708</t>
+          <t>-0.0018438490348602343 +/- 0.0010323522251321664</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.00164217804667246 +/- 0.0013268313384810595</t>
+          <t>-0.003975799481417431 +/- 0.0011291223245327253</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0035724575050418038 +/- 0.0013088812090579637</t>
+          <t>-0.004580812445980953 +/- 0.0013723428826061188</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00046096225871504747 +/- 0.0003457216940363087</t>
+          <t>-2.8810141169643978e-05 +/- 0.00039607395807744967</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00028810141169688386 +/- 0.0016995541577358314</t>
+          <t>-0.004811293575338471 +/- 0.0013819861659707757</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.008210890233362167 +/- 0.0015312800075964548</t>
+          <t>-0.009824258138864849 +/- 0.0013355605861710474</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0033707865168539075 +/- 0.0009984283175547967</t>
+          <t>0.00046096225871509187 +/- 0.0012304325268834722</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.003053874963987302 +/- 0.0014814128645557307</t>
+          <t>0.0010371650821089484 +/- 0.0006962285205182762</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.002909824258138849 +/- 0.0017498455360484093</t>
+          <t>-0.001613367905502694 +/- 0.0013025242933399324</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0002592912705272177 +/- 0.000416503379279758</t>
+          <t>-0.0007490636704119424 +/- 0.000502321975631317</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.007577067127628912 +/- 0.0007179450184026212</t>
+          <t>-0.004494382022471865 +/- 0.0018411461029870988</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.0025641025641025663 +/- 0.0013417609936266376</t>
+          <t>-0.005617977528089846 +/- 0.001424573358118826</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.009564966868337677 +/- 0.001374458132166689</t>
+          <t>-0.009881878421204216 +/- 0.0017715308717537537</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0012388360702967338 +/- 0.0012627258427433626</t>
+          <t>-0.00867185249207717 +/- 0.0021110187383143043</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0014405070584845748 +/- 0.0005762028233938344</t>
+          <t>0.0004321521175454035 +/- 0.0005193822062034209</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00023048112935751818 +/- 0.001021034004417692</t>
+          <t>-0.0011524056467876354 +/- 0.0009641717390193907</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.0027369634111207297 +/- 0.0018770862724588808</t>
+          <t>-0.01587438778450011 +/- 0.0019685992861834035</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0037741284932296336 +/- 0.0013167841984472893</t>
+          <t>-0.00642466148084121 +/- 0.0018040302165892612</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.0013828867761451647 +/- 0.0005435886564135265</t>
+          <t>-0.0008354940939210076 +/- 0.0006104759464251532</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0008354940939210409 +/- 0.0007225546645914528</t>
+          <t>-0.0014981273408239293 +/- 0.0004956684106622064</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.006107749927974637 +/- 0.0014735478942719067</t>
+          <t>0.001843849034860312 +/- 0.0013768715811407202</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>-0.0026217228464419763 +/- 0.0015160267492852705</t>
+          <t>-0.0019878997407086763 +/- 0.0006750431872002344</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.0006050129645635116 +/- 0.0008875207030106406</t>
+          <t>-0.00034572169403626065 +/- 0.000587613888054481</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.004494382022471888 +/- 0.0013340059813068477</t>
+          <t>0.0033131662345145863 +/- 0.0015420828223650352</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.006511091904350341 +/- 0.001670988187842138</t>
+          <t>-0.010861423220973743 +/- 0.0010860315082092179</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.005906078939786808 +/- 0.001710507359123875</t>
+          <t>-0.005243445692883863 +/- 0.0016133679055027371</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.011380005762028267 +/- 0.001040760119169598</t>
+          <t>-0.0121002592912705 +/- 0.0008926495756168134</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0017286084701815141 +/- 0.001508067107842402</t>
+          <t>-0.0004033419763756374 +/- 0.0015201274512558825</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.0069720541630654 +/- 0.002032289494502841</t>
+          <t>-0.003341976375684208 +/- 0.0009572600245368043</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.009392106021319513 +/- 0.001210025929127054</t>
+          <t>-0.006972054163065377 +/- 0.0017843690656527977</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.0005762028233938455 +/- 0.0008349972196018102</t>
+          <t>-0.0009507346585997944 +/- 0.0005320134057222564</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.0032267358110054877 +/- 0.0011437299476392388</t>
+          <t>-0.007058484586574432 +/- 0.0012172071549569146</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.015471045808124495 +/- 0.0009816609067934867</t>
+          <t>-0.01426101987899736 +/- 0.0012900382124597088</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.02633246902909825 +/- 0.0021644067958505172</t>
+          <t>-0.02376836646499565 +/- 0.001244184550947217</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.009737827715355817 +/- 0.00115815334152935</t>
+          <t>-0.013079804091040014 +/- 0.0014066903619399107</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0004897723998847469 +/- 0.0006318557245595393</t>
+          <t>0.000806683952751408 +/- 0.0005121402718130554</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.0008643042350907404 +/- 0.0007173667299330666</t>
+          <t>0.00011524056467879796 +/- 0.0006205894332624158</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.001152405646787691 +/- 0.00048208586950970533</t>
+          <t>-0.0006914433880725656 +/- 0.0002938069440272558</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.01607605877268802 +/- 0.0014393541915063922</t>
+          <t>-0.03295880149812732 +/- 0.0017769108550975902</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.019273984442523782 +/- 0.0013662812678051682</t>
+          <t>-0.025151253241140835 +/- 0.001314260412325777</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.0013540766349754985 +/- 0.00044725366454219774</t>
+          <t>-8.643042350903185e-05 +/- 0.000805139073032679</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.003111495246326723 +/- 0.0004425897866821417</t>
+          <t>-0.00028810141169688386 +/- 0.0009812380504711298</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.01685393258426967 +/- 0.0020094944387751995</t>
+          <t>-0.01541342552578504 +/- 0.001224007247839126</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.0004897723998847359 +/- 0.0007062892925457358</t>
+          <t>-0.0004897723998847136 +/- 0.00036555971018294327</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0037453183520599455 +/- 0.001070249243503698</t>
+          <t>-0.005358686257562606 +/- 0.0017439061884669182</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.027945836934601 +/- 0.002361728785009425</t>
+          <t>-0.034658599827139126 +/- 0.0019112657206133126</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.0005473926822241237 +/- 0.001488400040690258</t>
+          <t>-0.0075482569864592005 +/- 0.0018166387519947431</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.006655142610198761 +/- 0.0010181847909577707</t>
+          <t>-0.00011524056467873133 +/- 0.0012371599281811446</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.001065975223278559 +/- 0.0004472536645422157</t>
+          <t>0.00017286084701818584 +/- 0.00019110485683410464</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.0075194468452895345 +/- 0.0012388360702967535</t>
+          <t>0.0036012676462115144 +/- 0.001584557764333049</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.0008643042350907293 +/- 0.0007622446877166864</t>
+          <t>0.0009219245174301727 +/- 0.0009710342579287144</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.003601267646211437 +/- 0.0013589716410338148</t>
+          <t>0.0007202535292423317 +/- 0.0012172071549569525</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.006856813598386624 +/- 0.0010451372599952222</t>
+          <t>0.004868913857677948 +/- 0.0013293312584338136</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.005012964563526323 +/- 0.001531008960597689</t>
+          <t>0.0006338231057332555 +/- 0.001053049085710006</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.007173725151253229 +/- 0.0015698222674532358</t>
+          <t>-0.0038605589167386434 +/- 0.0014416590035375059</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.0004033419763756485 +/- 0.00032081615458541204</t>
+          <t>-0.00014405070584844193 +/- 0.0001932643022903656</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.005617977528089879 +/- 0.0012835879809821773</t>
+          <t>0.00037453183520604896 +/- 0.0005769226273264483</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0023624315759147143 +/- 0.0010291311494953494</t>
+          <t>0.0010659752232786367 +/- 0.000855132358378336</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.003457216940363006 +/- 0.0008249968921507562</t>
+          <t>0.0020455200230481306 +/- 0.0006750431872002301</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.004350331316623435 +/- 0.001801267534697856</t>
+          <t>0.002189570728896617 +/- 0.0010242805436261081</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0003745318352059712 +/- 0.000855132358378317</t>
+          <t>0.0007778738115817307 +/- 0.0005161761125660957</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0023912417170843915 +/- 0.0013638490784839638</t>
+          <t>0.0010371650821089373 +/- 0.001441659003537526</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0015557476231633284 +/- 0.0013277693600464327</t>
+          <t>0.004091040046096261 +/- 0.0013500863744004793</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.0017574186113511804 +/- 0.001265352420397438</t>
+          <t>0.003111495246326745 +/- 0.001143729947639259</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.004638432728320352 +/- 0.000675043187200233</t>
+          <t>-0.002708153269950975 +/- 0.0012767801674537723</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.0034284067991932955 +/- 0.0015214918958814186</t>
+          <t>0.0028233938346298284 +/- 0.0016287287842238576</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0006050129645635116 +/- 0.0011769921184566808</t>
+          <t>-0.0033707865168538854 +/- 0.0011670774474519675</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.000684116597263551 +/- 0.001950684405957121</t>
+          <t>-0.0007733491969066031 +/- 0.0016677984258032354</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.00461035098155862 +/- 0.0016627513217577431</t>
+          <t>-0.0003866745984533071 +/- 0.0017549077929803801</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.001992861392028533 +/- 0.0015458401499329312</t>
+          <t>0.00011897679952407313 +/- 0.0010060401264299693</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.003807257584770951 +/- 0.001037215691502841</t>
+          <t>0.005710886377156432 +/- 0.0008285775298741378</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0026769779892921062 +/- 0.0012478392006783588</t>
+          <t>-0.0016954193932183447 +/- 0.0010892226902796346</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0006246281975015089 +/- 0.001631598828304866</t>
+          <t>0.004074955383700185 +/- 0.0014143359224234135</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0006246281975014756 +/- 0.0004878411501147187</t>
+          <t>0.0001487209994051053 +/- 0.00023980540595770284</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.0060083283759667094 +/- 0.0011732946414822164</t>
+          <t>0.00035693039857226383 +/- 0.002689507330269457</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.032807852468768564 +/- 0.0022379422136795733</t>
+          <t>0.018352171326591282 +/- 0.003738906264820021</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.0212968471148126 +/- 0.00240615686093476</t>
+          <t>0.026710291493158834 +/- 0.0030962554859424378</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.002706722189173072 +/- 0.0008460120555221711</t>
+          <t>0.0013384889946460254 +/- 0.001235369402575554</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.001903628792385459 +/- 0.0016888839460533537</t>
+          <t>0.0008625817965496552 +/- 0.0014958109411873975</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.009012492563950003 +/- 0.001999951870792885</t>
+          <t>0.0034503271861986984 +/- 0.0017404805280580404</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.0229625223081499 +/- 0.002164593146776952</t>
+          <t>0.021653777513384875 +/- 0.0016867872550574562</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.026591314693634727 +/- 0.0016410605858576746</t>
+          <t>0.03152885187388458 +/- 0.003009901401706974</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0017549077929803424 +/- 0.0017918257563151682</t>
+          <t>0.0013087447947650154 +/- 0.001297883654329056</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.0012790005948839721 +/- 0.0019687425036731664</t>
+          <t>-0.002676977989292084 +/- 0.001310096106219218</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0018441403926234058 +/- 0.001158115546337411</t>
+          <t>0.0014574657941701207 +/- 0.0012650904412930966</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.0017251635930993436 +/- 0.0012030784304673697</t>
+          <t>-0.003301606186793582 +/- 0.001593189975115061</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.9744199881021062e-05 +/- 0.0002470738805150945</t>
+          <t>0.0 +/- 0.00026604021148121697</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.005175490779298053 +/- 0.0012205999124737135</t>
+          <t>-0.004521118381915545 +/- 0.0011657298002537325</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-5.948839976207543e-05 +/- 0.0011033454486015142</t>
+          <t>0.002736466389054115 +/- 0.0008069399147085494</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0020226055919095654 +/- 0.0010707911957168212</t>
+          <t>0.0013979773944080786 +/- 0.001269279493953116</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0032718619869125274 +/- 0.0016072880530762946</t>
+          <t>0.0002082093991671474 +/- 0.0006657652970136511</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0065734681737061205 +/- 0.0018501274884097656</t>
+          <t>0.0031826293872694754 +/- 0.0010810697112067981</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-2.9744199881043264e-05 +/- 0.00040891514232205717</t>
+          <t>0.0005948839976204434 +/- 0.0006651005287030723</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.003747769185008909 +/- 0.0012350112725774435</t>
+          <t>0.0055026769779892735 +/- 0.0014946275462702017</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.002676977989292062 +/- 0.0013033255383823133</t>
+          <t>0.0043426531826293744 +/- 0.0006808758561724813</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0017549077929803647 +/- 0.001319851738984764</t>
+          <t>0.0023497917906008083 +/- 0.0011706525076832027</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.001160023795359888 +/- 0.0012995866909549848</t>
+          <t>0.001516954193932174 +/- 0.00117818574184049</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0006543723973824967 +/- 0.0007959005449291739</t>
+          <t>0.0004164187983342948 +/- 0.000518607845751426</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.0002974419988102217 +/- 0.0006095747035073953</t>
+          <t>-0.001100535395597868 +/- 0.0004216968137643654</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.000654372397382541 +/- 0.0009196683422808006</t>
+          <t>0.0009815585960737505 +/- 0.001226745426966167</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.0016359309934562472 +/- 0.0018202381059838513</t>
+          <t>0.0027364663890541373 +/- 0.0014437431409294102</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.0005056513979773802 +/- 0.000565139797739433</t>
+          <t>0.00020820939916713633 +/- 0.0005956271384443849</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.00011897679952410645 +/- 0.0008003345655606025</t>
+          <t>0.0031528851873884544 +/- 0.000582864900126875</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0005353955978583902 +/- 0.001335511262382136</t>
+          <t>-0.0015764425936942272 +/- 0.0016075632500739542</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0001487209994050942 +/- 0.0006684177589007839</t>
+          <t>0.004253420582986289 +/- 0.0010047201519366156</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.948839976208653e-05 +/- 0.0009002228405961867</t>
+          <t>-0.0005056513979773914 +/- 0.0006102999562368576</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.003182629387269431 +/- 0.0012267454269661677</t>
+          <t>-0.005324211778703181 +/- 0.001821209936328578</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.0020226055919095763 +/- 0.001028650592848923</t>
+          <t>0.004193932183224269 +/- 0.0011554387031264296</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0005948839976204434 +/- 0.0010558143574835557</t>
+          <t>0.0006246281975014756 +/- 0.0012439335910961675</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.005770374776918508 +/- 0.0009702264384473828</t>
+          <t>-0.01796549672813803 +/- 0.002222670040722135</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0013384889946460143 +/- 0.0021042838971831184</t>
+          <t>0.006989886972040449 +/- 0.001887057932844956</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.007822724568709083 +/- 0.0017749588040256673</t>
+          <t>0.003985722784057089 +/- 0.0008221460417064266</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0017846519928613857 +/- 0.0011365242816503802</t>
+          <t>0.003747769185008909 +/- 0.0010234771287379926</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.00017846519928613747 +/- 0.0004248321492291957</t>
+          <t>0.0002974419988102106 +/- 0.00039906031722182543</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.0003866745984532738 +/- 0.001144668733188194</t>
+          <t>-0.003866745984533004 +/- 0.0009865035069468928</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0159131469363474 +/- 0.0014827416514710888</t>
+          <t>2.974419988100996e-05 +/- 0.0009633631612553063</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.008239143367043433 +/- 0.0015401063017251172</t>
+          <t>-0.002111838191552673 +/- 0.0016477857209357004</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.0016061867935752705 +/- 0.002562838694650565</t>
+          <t>-0.010410469958358138 +/- 0.002030463791299944</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.0003866745984532849 +/- 0.000565139797739451</t>
+          <t>-0.0010113027959547938 +/- 0.0005353955978584235</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0004461629982153714 +/- 0.0006684177589007791</t>
+          <t>-0.00023795359904820178 +/- 0.0005612124409313848</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.000297441998810255 +/- 0.00032583138459559485</t>
+          <t>0.0006246281975014645 +/- 0.00036307423009321793</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.01186793575252828 +/- 0.001771965616728923</t>
+          <t>-0.0071088637715645666 +/- 0.001265090441293086</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.010707911957168326 +/- 0.0017896024933362579</t>
+          <t>-0.0019631171921475456 +/- 0.0016993285969167755</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0006246281975014645 +/- 0.0004878411501147127</t>
+          <t>-0.0005651397977394668 +/- 0.0006160712426296264</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.0006246281975014978 +/- 0.0010169732895466375</t>
+          <t>0.003004164187983305 +/- 0.0012296268059842218</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.008477096966091623 +/- 0.001476762830137576</t>
+          <t>-0.005889351576442614 +/- 0.0010541371294866104</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>8.923259964305208e-05 +/- 0.00097794659266946</t>
+          <t>-2.9744199881021062e-05 +/- 0.0006015392152336914</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.0004759071980963703 +/- 0.001558096472779151</t>
+          <t>-0.004074955383700185 +/- 0.0009316156908605459</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0061570493753718035 +/- 0.0016880979921074094</t>
+          <t>-0.008417608566329582 +/- 0.001505244607838182</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.0016359309934562694 +/- 0.0009522790359061458</t>
+          <t>-0.0024092801903628945 +/- 0.0019434141848803917</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0040154669839381095 +/- 0.000952279035906132</t>
+          <t>-0.002974419988102317 +/- 0.0012965196143785527</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-0.00041641879833436145 +/- 0.00038091161436247495</t>
+          <t>-0.00041641879833430594 +/- 0.00023795359904819067</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.0038072575847709843 +/- 0.0010200135752220208</t>
+          <t>0.00011897679952408425 +/- 0.0011302795954788675</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.0006246281975014978 +/- 0.0008868561282495893</t>
+          <t>-0.0015466983938132394 +/- 0.0007733491969065963</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.0004461629982153159 +/- 0.000484200493637713</t>
+          <t>-0.001457465794170143 +/- 0.0005395109205002077</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.007317073170731691 +/- 0.001730284303658422</t>
+          <t>0.00517549077929802 +/- 0.0012350112725774518</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.004402141582391439 +/- 0.001374684117583728</t>
+          <t>-0.000743604997025582 +/- 0.0017609470690797995</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.008209399167162401 +/- 0.00104062199194145</t>
+          <t>0.005740630577037465 +/- 0.0013437664483137088</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002974419988102106</t>
+          <t>-0.0003569303985722527 +/- 0.0002225852103970061</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.0003569303985722527 +/- 0.000919668342280802</t>
+          <t>-0.00026769779892921175 +/- 0.0005056513979773854</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.0011005353955978459 +/- 0.0007412216415453494</t>
+          <t>-0.00017846519928613747 +/- 0.000464619254961712</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.0008328375966686341 +/- 0.0007382316267692267</t>
+          <t>0.0009220701963116972 +/- 0.00033782916988700897</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.0007138607971445832 +/- 0.0011065481997464635</t>
+          <t>0.00047590719809634805 +/- 0.001540967739082513</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.00026769779892917846 +/- 0.0005556675101805128</t>
+          <t>0.0021415823914336498 +/- 0.0006210771272403829</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.003033908387864359 +/- 0.0009480890809345017</t>
+          <t>-0.0013682331945270687 +/- 0.0008328375966686436</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0005651397977394224 +/- 0.0014105777158095673</t>
+          <t>-0.0007138607971445609 +/- 0.0011535228691056108</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0003271861986912317 +/- 0.0006015392152336859</t>
+          <t>-8.923259964308539e-05 +/- 0.000498603647062469</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.0020226055919095763 +/- 0.0007847058868693042</t>
+          <t>-0.0008625817965496774 +/- 0.0013659681740874373</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.0017549077929803758 +/- 0.0009633631612552962</t>
+          <t>0.0034205829863176553 +/- 0.0016031544292935069</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.004253420582986301 +/- 0.0008828567566719754</t>
+          <t>-0.00258774538964901 +/- 0.0008625817965496597</t>
         </is>
       </c>
     </row>
